--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DB10C10-D83E-4C7F-BF7A-D2B7E37BFA20}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C08B5072-BF17-4F9A-8DB4-67908CFB0F33}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="2085" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -1596,7 +1596,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1638,18 +1638,33 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1695,7 +1710,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1981,7 +2001,7 @@
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7222,7 +7242,7 @@
       <c r="A477" s="4">
         <v>1010084035</v>
       </c>
-      <c r="B477" s="4" t="s">
+      <c r="B477" s="17" t="s">
         <v>479</v>
       </c>
       <c r="C477" s="5" t="s">
@@ -7233,10 +7253,10 @@
       <c r="A478" s="2">
         <v>1010062826</v>
       </c>
-      <c r="B478" s="15" t="s">
+      <c r="B478" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="C478" s="17" t="s">
+      <c r="C478" s="5" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7244,10 +7264,10 @@
       <c r="A479" s="15">
         <v>1010002592</v>
       </c>
-      <c r="B479" s="15" t="s">
+      <c r="B479" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="C479" s="17" t="s">
+      <c r="C479" s="5" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7255,10 +7275,10 @@
       <c r="A480" s="16">
         <v>1010001155</v>
       </c>
-      <c r="B480" s="15" t="s">
+      <c r="B480" s="18" t="s">
         <v>486</v>
       </c>
-      <c r="C480" s="17" t="s">
+      <c r="C480" s="5" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7266,10 +7286,10 @@
       <c r="A481" s="15">
         <v>1010001062</v>
       </c>
-      <c r="B481" s="15" t="s">
+      <c r="B481" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="C481" s="17" t="s">
+      <c r="C481" s="5" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7277,10 +7297,10 @@
       <c r="A482" s="15">
         <v>1010084328</v>
       </c>
-      <c r="B482" s="15" t="s">
+      <c r="B482" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="C482" s="17" t="s">
+      <c r="C482" s="5" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7288,10 +7308,10 @@
       <c r="A483" s="16">
         <v>1010044502</v>
       </c>
-      <c r="B483" s="15" t="s">
+      <c r="B483" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="C483" s="17" t="s">
+      <c r="C483" s="5" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7299,10 +7319,10 @@
       <c r="A484" s="15">
         <v>1010053692</v>
       </c>
-      <c r="B484" s="15" t="s">
+      <c r="B484" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="C484" s="17" t="s">
+      <c r="C484" s="5" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7310,10 +7330,10 @@
       <c r="A485" s="15">
         <v>390742</v>
       </c>
-      <c r="B485" s="15" t="s">
+      <c r="B485" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="C485" s="17" t="s">
+      <c r="C485" s="5" t="s">
         <v>492</v>
       </c>
     </row>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C08B5072-BF17-4F9A-8DB4-67908CFB0F33}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1758C6C7-39E7-436B-86AB-DAD646AC867C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -1413,9 +1413,6 @@
     <t xml:space="preserve">VASELINA VEGETAL 3KG </t>
   </si>
   <si>
-    <t>borracharia</t>
-  </si>
-  <si>
     <t>DISCO CORTE 7 POLEGADAS DEWALT</t>
   </si>
   <si>
@@ -1516,6 +1513,9 @@
   </si>
   <si>
     <t>Operação Pluma</t>
+  </si>
+  <si>
+    <t>Borracharia</t>
   </si>
 </sst>
 </file>
@@ -2006,7 +2006,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>425</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2034,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2045,7 +2045,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2056,7 +2056,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2067,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2078,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2089,7 +2089,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2111,7 +2111,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2122,7 +2122,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2133,7 +2133,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2144,7 +2144,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2155,7 +2155,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2166,7 +2166,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2177,7 +2177,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2188,7 +2188,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2199,7 +2199,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2210,7 +2210,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2221,7 +2221,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2243,7 +2243,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2254,7 +2254,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2265,7 +2265,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2276,7 +2276,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2287,7 +2287,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2298,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2309,7 +2309,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2320,7 +2320,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2331,7 +2331,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2342,7 +2342,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2353,7 +2353,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2364,7 +2364,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2375,7 +2375,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2386,7 +2386,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2397,7 +2397,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2408,7 +2408,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2419,7 +2419,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2430,7 +2430,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2441,7 +2441,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2452,7 +2452,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2463,7 +2463,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2474,7 +2474,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2485,7 +2485,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2496,7 +2496,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2507,7 +2507,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2529,7 +2529,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2540,7 +2540,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2551,7 +2551,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2562,7 +2562,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2573,7 +2573,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2584,7 +2584,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2595,7 +2595,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2606,7 +2606,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2617,7 +2617,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2628,7 +2628,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2639,7 +2639,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2650,7 +2650,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2661,7 +2661,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2672,7 +2672,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2683,7 +2683,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2694,7 +2694,7 @@
         <v>61</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2705,7 +2705,7 @@
         <v>62</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2716,7 +2716,7 @@
         <v>63</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2727,7 +2727,7 @@
         <v>64</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2738,7 +2738,7 @@
         <v>65</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2749,7 +2749,7 @@
         <v>66</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2760,7 +2760,7 @@
         <v>67</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2771,7 +2771,7 @@
         <v>68</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2782,7 +2782,7 @@
         <v>69</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2793,7 +2793,7 @@
         <v>70</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2804,7 +2804,7 @@
         <v>71</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2815,7 +2815,7 @@
         <v>72</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2826,7 +2826,7 @@
         <v>428</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2837,7 +2837,7 @@
         <v>73</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2848,7 +2848,7 @@
         <v>74</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2859,7 +2859,7 @@
         <v>75</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2870,7 +2870,7 @@
         <v>76</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2881,7 +2881,7 @@
         <v>77</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2892,7 +2892,7 @@
         <v>78</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2903,7 +2903,7 @@
         <v>79</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2914,7 +2914,7 @@
         <v>80</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2925,7 +2925,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>82</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2947,7 +2947,7 @@
         <v>83</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2958,7 +2958,7 @@
         <v>84</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2969,7 +2969,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2980,7 +2980,7 @@
         <v>86</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2991,7 +2991,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
         <v>88</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3013,7 +3013,7 @@
         <v>89</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3024,7 +3024,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3035,7 +3035,7 @@
         <v>91</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3046,7 +3046,7 @@
         <v>92</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3057,7 +3057,7 @@
         <v>93</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3068,7 +3068,7 @@
         <v>94</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3079,7 +3079,7 @@
         <v>95</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3090,7 +3090,7 @@
         <v>96</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3101,7 +3101,7 @@
         <v>97</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3112,7 +3112,7 @@
         <v>98</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3123,7 +3123,7 @@
         <v>99</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3134,7 +3134,7 @@
         <v>100</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3145,7 +3145,7 @@
         <v>101</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3156,7 +3156,7 @@
         <v>102</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3167,7 +3167,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3178,7 +3178,7 @@
         <v>104</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3189,7 +3189,7 @@
         <v>105</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3200,7 +3200,7 @@
         <v>106</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3211,7 +3211,7 @@
         <v>107</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3222,7 +3222,7 @@
         <v>108</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3233,7 +3233,7 @@
         <v>109</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3244,7 +3244,7 @@
         <v>110</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3255,7 +3255,7 @@
         <v>111</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3266,7 +3266,7 @@
         <v>112</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3277,7 +3277,7 @@
         <v>113</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3288,7 +3288,7 @@
         <v>114</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3299,7 +3299,7 @@
         <v>115</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3310,7 +3310,7 @@
         <v>116</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3321,7 +3321,7 @@
         <v>117</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3332,7 +3332,7 @@
         <v>118</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3343,7 +3343,7 @@
         <v>119</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>120</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3365,7 +3365,7 @@
         <v>121</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3376,7 +3376,7 @@
         <v>122</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3387,7 +3387,7 @@
         <v>123</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
         <v>124</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3409,7 +3409,7 @@
         <v>125</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3420,7 +3420,7 @@
         <v>126</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3431,7 +3431,7 @@
         <v>127</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3442,7 +3442,7 @@
         <v>128</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3453,7 +3453,7 @@
         <v>129</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3464,7 +3464,7 @@
         <v>130</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3475,7 +3475,7 @@
         <v>131</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3486,7 +3486,7 @@
         <v>132</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3497,7 +3497,7 @@
         <v>133</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3508,7 +3508,7 @@
         <v>134</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3519,7 +3519,7 @@
         <v>135</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3530,7 +3530,7 @@
         <v>136</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3541,7 +3541,7 @@
         <v>137</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3552,7 +3552,7 @@
         <v>138</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3563,7 +3563,7 @@
         <v>139</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3574,7 +3574,7 @@
         <v>140</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3585,7 +3585,7 @@
         <v>141</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3596,7 +3596,7 @@
         <v>142</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3607,7 +3607,7 @@
         <v>143</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3618,7 +3618,7 @@
         <v>144</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3629,7 +3629,7 @@
         <v>145</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3640,7 +3640,7 @@
         <v>146</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3651,7 +3651,7 @@
         <v>147</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3662,7 +3662,7 @@
         <v>148</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3673,7 +3673,7 @@
         <v>149</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3684,7 +3684,7 @@
         <v>150</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3695,7 +3695,7 @@
         <v>151</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3706,7 +3706,7 @@
         <v>152</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3717,7 +3717,7 @@
         <v>153</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3728,7 +3728,7 @@
         <v>426</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3739,7 +3739,7 @@
         <v>427</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3750,7 +3750,7 @@
         <v>154</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3761,7 +3761,7 @@
         <v>155</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>156</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3783,7 +3783,7 @@
         <v>157</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3794,7 +3794,7 @@
         <v>158</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3805,7 +3805,7 @@
         <v>159</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3816,7 +3816,7 @@
         <v>160</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3827,7 +3827,7 @@
         <v>161</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3838,7 +3838,7 @@
         <v>162</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3849,7 +3849,7 @@
         <v>163</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3860,7 +3860,7 @@
         <v>164</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3871,7 +3871,7 @@
         <v>165</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3882,7 +3882,7 @@
         <v>166</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
         <v>167</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3904,7 +3904,7 @@
         <v>168</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3915,7 +3915,7 @@
         <v>169</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
         <v>170</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3937,7 +3937,7 @@
         <v>171</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3948,7 +3948,7 @@
         <v>172</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3959,7 +3959,7 @@
         <v>173</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3970,7 +3970,7 @@
         <v>174</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3981,7 +3981,7 @@
         <v>175</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3992,7 +3992,7 @@
         <v>176</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4003,7 +4003,7 @@
         <v>177</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4014,7 +4014,7 @@
         <v>178</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>179</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4036,7 +4036,7 @@
         <v>180</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4047,7 +4047,7 @@
         <v>181</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4058,7 +4058,7 @@
         <v>182</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4069,7 +4069,7 @@
         <v>183</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4080,7 +4080,7 @@
         <v>184</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4091,7 +4091,7 @@
         <v>185</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4102,7 +4102,7 @@
         <v>186</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4113,7 +4113,7 @@
         <v>187</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4124,7 +4124,7 @@
         <v>188</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4135,7 +4135,7 @@
         <v>189</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4146,7 +4146,7 @@
         <v>190</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4157,7 +4157,7 @@
         <v>191</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4168,7 +4168,7 @@
         <v>192</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4179,7 +4179,7 @@
         <v>193</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>194</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4201,7 +4201,7 @@
         <v>195</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4212,7 +4212,7 @@
         <v>196</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4223,7 +4223,7 @@
         <v>197</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4234,7 +4234,7 @@
         <v>198</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4245,7 +4245,7 @@
         <v>199</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4256,7 +4256,7 @@
         <v>200</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4267,7 +4267,7 @@
         <v>201</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4278,7 +4278,7 @@
         <v>202</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4289,7 +4289,7 @@
         <v>203</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4300,7 +4300,7 @@
         <v>204</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4311,7 +4311,7 @@
         <v>205</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4322,7 +4322,7 @@
         <v>206</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>207</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4344,7 +4344,7 @@
         <v>208</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4355,7 +4355,7 @@
         <v>209</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4366,7 +4366,7 @@
         <v>210</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4377,7 +4377,7 @@
         <v>211</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4388,7 +4388,7 @@
         <v>212</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4399,7 +4399,7 @@
         <v>213</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4410,7 +4410,7 @@
         <v>214</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>215</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4432,7 +4432,7 @@
         <v>216</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4443,7 +4443,7 @@
         <v>217</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4454,7 +4454,7 @@
         <v>218</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4465,7 +4465,7 @@
         <v>219</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4476,7 +4476,7 @@
         <v>220</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4487,7 +4487,7 @@
         <v>221</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4498,7 +4498,7 @@
         <v>222</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4509,7 +4509,7 @@
         <v>223</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4520,7 +4520,7 @@
         <v>224</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4531,7 +4531,7 @@
         <v>225</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4542,7 +4542,7 @@
         <v>226</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4553,7 +4553,7 @@
         <v>227</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4564,7 +4564,7 @@
         <v>228</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4575,7 +4575,7 @@
         <v>229</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4586,7 +4586,7 @@
         <v>230</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4597,7 +4597,7 @@
         <v>231</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>232</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4619,7 +4619,7 @@
         <v>233</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4630,7 +4630,7 @@
         <v>234</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4641,7 +4641,7 @@
         <v>235</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4652,7 +4652,7 @@
         <v>236</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4663,7 +4663,7 @@
         <v>237</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4674,7 +4674,7 @@
         <v>238</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4685,7 +4685,7 @@
         <v>239</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4696,7 +4696,7 @@
         <v>240</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4707,7 +4707,7 @@
         <v>241</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4718,7 +4718,7 @@
         <v>242</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4729,7 +4729,7 @@
         <v>243</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4740,7 +4740,7 @@
         <v>244</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4751,7 +4751,7 @@
         <v>245</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4762,7 +4762,7 @@
         <v>246</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>247</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4784,7 +4784,7 @@
         <v>248</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4795,7 +4795,7 @@
         <v>249</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4806,7 +4806,7 @@
         <v>250</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4817,7 +4817,7 @@
         <v>251</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4828,7 +4828,7 @@
         <v>252</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4839,7 +4839,7 @@
         <v>253</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4850,7 +4850,7 @@
         <v>254</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4861,7 +4861,7 @@
         <v>255</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4872,7 +4872,7 @@
         <v>256</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4883,7 +4883,7 @@
         <v>257</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4894,7 +4894,7 @@
         <v>258</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4905,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4916,7 +4916,7 @@
         <v>260</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4927,7 +4927,7 @@
         <v>261</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4938,7 +4938,7 @@
         <v>262</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4949,7 +4949,7 @@
         <v>263</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4960,7 +4960,7 @@
         <v>264</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4971,7 +4971,7 @@
         <v>265</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4982,7 +4982,7 @@
         <v>266</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>267</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5004,7 +5004,7 @@
         <v>268</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5015,7 +5015,7 @@
         <v>269</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>270</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5037,7 +5037,7 @@
         <v>271</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5048,7 +5048,7 @@
         <v>272</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5059,7 +5059,7 @@
         <v>273</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5070,7 +5070,7 @@
         <v>274</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5081,7 +5081,7 @@
         <v>275</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5092,7 +5092,7 @@
         <v>276</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5103,7 +5103,7 @@
         <v>277</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5114,7 +5114,7 @@
         <v>278</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5125,7 +5125,7 @@
         <v>279</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5136,7 +5136,7 @@
         <v>280</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5147,7 +5147,7 @@
         <v>281</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5158,7 +5158,7 @@
         <v>282</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5169,7 +5169,7 @@
         <v>283</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5180,7 +5180,7 @@
         <v>284</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5191,7 +5191,7 @@
         <v>285</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5202,7 +5202,7 @@
         <v>286</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5213,7 +5213,7 @@
         <v>287</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5224,7 +5224,7 @@
         <v>288</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5235,7 +5235,7 @@
         <v>289</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5246,7 +5246,7 @@
         <v>290</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5257,7 +5257,7 @@
         <v>291</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5268,7 +5268,7 @@
         <v>292</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5279,7 +5279,7 @@
         <v>293</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5290,7 +5290,7 @@
         <v>294</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5301,7 +5301,7 @@
         <v>295</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5312,7 +5312,7 @@
         <v>296</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5323,7 +5323,7 @@
         <v>297</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5334,7 +5334,7 @@
         <v>298</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5345,7 +5345,7 @@
         <v>299</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5356,7 +5356,7 @@
         <v>300</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5367,7 +5367,7 @@
         <v>301</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5378,7 +5378,7 @@
         <v>302</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5389,7 +5389,7 @@
         <v>304</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5400,7 +5400,7 @@
         <v>305</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5411,7 +5411,7 @@
         <v>306</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5422,7 +5422,7 @@
         <v>307</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5433,7 +5433,7 @@
         <v>308</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5444,7 +5444,7 @@
         <v>309</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>310</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5466,7 +5466,7 @@
         <v>311</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5477,7 +5477,7 @@
         <v>312</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5488,7 +5488,7 @@
         <v>313</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5499,7 +5499,7 @@
         <v>314</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5510,7 +5510,7 @@
         <v>315</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5521,7 +5521,7 @@
         <v>316</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5532,7 +5532,7 @@
         <v>317</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5543,7 +5543,7 @@
         <v>318</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5554,7 +5554,7 @@
         <v>319</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5565,7 +5565,7 @@
         <v>320</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5576,7 +5576,7 @@
         <v>321</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5587,7 +5587,7 @@
         <v>322</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5598,7 +5598,7 @@
         <v>323</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5609,7 +5609,7 @@
         <v>324</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5620,7 +5620,7 @@
         <v>325</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5631,7 +5631,7 @@
         <v>326</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5642,7 +5642,7 @@
         <v>327</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>328</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5664,7 +5664,7 @@
         <v>329</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5673,7 +5673,7 @@
         <v>330</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5684,7 +5684,7 @@
         <v>331</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5695,7 +5695,7 @@
         <v>332</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5706,7 +5706,7 @@
         <v>333</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5717,7 +5717,7 @@
         <v>334</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5728,7 +5728,7 @@
         <v>335</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5739,7 +5739,7 @@
         <v>336</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5750,7 +5750,7 @@
         <v>337</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5761,7 +5761,7 @@
         <v>338</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5772,7 +5772,7 @@
         <v>429</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5783,7 +5783,7 @@
         <v>339</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5794,7 +5794,7 @@
         <v>340</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5805,7 +5805,7 @@
         <v>341</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5816,7 +5816,7 @@
         <v>342</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5827,7 +5827,7 @@
         <v>343</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5838,7 +5838,7 @@
         <v>344</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5849,7 +5849,7 @@
         <v>345</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5860,7 +5860,7 @@
         <v>346</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5871,7 +5871,7 @@
         <v>347</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5882,7 +5882,7 @@
         <v>348</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5893,7 +5893,7 @@
         <v>349</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5904,7 +5904,7 @@
         <v>350</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5915,7 +5915,7 @@
         <v>351</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5926,7 +5926,7 @@
         <v>352</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5937,7 +5937,7 @@
         <v>353</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5948,7 +5948,7 @@
         <v>354</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5959,7 +5959,7 @@
         <v>355</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5970,7 +5970,7 @@
         <v>356</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5981,7 +5981,7 @@
         <v>357</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5992,7 +5992,7 @@
         <v>358</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6003,7 +6003,7 @@
         <v>359</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6014,7 +6014,7 @@
         <v>360</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6025,7 +6025,7 @@
         <v>361</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6036,7 +6036,7 @@
         <v>362</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6047,7 +6047,7 @@
         <v>363</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6058,7 +6058,7 @@
         <v>364</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6069,7 +6069,7 @@
         <v>365</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6080,7 +6080,7 @@
         <v>366</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6091,7 +6091,7 @@
         <v>367</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6102,7 +6102,7 @@
         <v>368</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6113,7 +6113,7 @@
         <v>369</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6124,7 +6124,7 @@
         <v>370</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6135,7 +6135,7 @@
         <v>371</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6146,7 +6146,7 @@
         <v>372</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6157,7 +6157,7 @@
         <v>373</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6168,7 +6168,7 @@
         <v>374</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6179,7 +6179,7 @@
         <v>375</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6190,7 +6190,7 @@
         <v>376</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6201,7 +6201,7 @@
         <v>377</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6212,7 +6212,7 @@
         <v>378</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6223,7 +6223,7 @@
         <v>379</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6234,7 +6234,7 @@
         <v>380</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6245,7 +6245,7 @@
         <v>381</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6256,7 +6256,7 @@
         <v>382</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6267,7 +6267,7 @@
         <v>383</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6278,7 +6278,7 @@
         <v>384</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6289,7 +6289,7 @@
         <v>385</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6300,7 +6300,7 @@
         <v>386</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6311,7 +6311,7 @@
         <v>387</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6322,7 +6322,7 @@
         <v>388</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6333,7 +6333,7 @@
         <v>389</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6344,7 +6344,7 @@
         <v>390</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6355,7 +6355,7 @@
         <v>391</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6366,7 +6366,7 @@
         <v>392</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6377,7 +6377,7 @@
         <v>393</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6388,7 +6388,7 @@
         <v>394</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6399,7 +6399,7 @@
         <v>395</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6410,7 +6410,7 @@
         <v>396</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6421,7 +6421,7 @@
         <v>397</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6432,7 +6432,7 @@
         <v>398</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6443,7 +6443,7 @@
         <v>399</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6454,7 +6454,7 @@
         <v>400</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6465,7 +6465,7 @@
         <v>401</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6476,7 +6476,7 @@
         <v>402</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6487,7 +6487,7 @@
         <v>403</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6498,7 +6498,7 @@
         <v>404</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6509,7 +6509,7 @@
         <v>405</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6520,7 +6520,7 @@
         <v>406</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6531,7 +6531,7 @@
         <v>407</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6542,7 +6542,7 @@
         <v>408</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>409</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6564,7 +6564,7 @@
         <v>410</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6575,7 +6575,7 @@
         <v>411</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6586,7 +6586,7 @@
         <v>412</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6597,7 +6597,7 @@
         <v>413</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6608,7 +6608,7 @@
         <v>414</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6619,7 +6619,7 @@
         <v>415</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6630,7 +6630,7 @@
         <v>416</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6641,7 +6641,7 @@
         <v>417</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6652,7 +6652,7 @@
         <v>418</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6663,7 +6663,7 @@
         <v>419</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6674,7 +6674,7 @@
         <v>420</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6685,7 +6685,7 @@
         <v>421</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6696,7 +6696,7 @@
         <v>422</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6707,7 +6707,7 @@
         <v>423</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6718,7 +6718,7 @@
         <v>424</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6729,7 +6729,7 @@
         <v>431</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6740,7 +6740,7 @@
         <v>432</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6751,7 +6751,7 @@
         <v>433</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6762,7 +6762,7 @@
         <v>434</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6773,7 +6773,7 @@
         <v>435</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6784,7 +6784,7 @@
         <v>436</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6795,7 +6795,7 @@
         <v>437</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6806,7 +6806,7 @@
         <v>438</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6817,7 +6817,7 @@
         <v>439</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6828,7 +6828,7 @@
         <v>440</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6839,7 +6839,7 @@
         <v>441</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6850,7 +6850,7 @@
         <v>442</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6861,7 +6861,7 @@
         <v>443</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6872,7 +6872,7 @@
         <v>444</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6883,7 +6883,7 @@
         <v>445</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6894,7 +6894,7 @@
         <v>446</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6905,7 +6905,7 @@
         <v>447</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6916,7 +6916,7 @@
         <v>448</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6927,7 +6927,7 @@
         <v>449</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6938,7 +6938,7 @@
         <v>450</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6949,7 +6949,7 @@
         <v>451</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6960,7 +6960,7 @@
         <v>452</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6971,7 +6971,7 @@
         <v>453</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6982,7 +6982,7 @@
         <v>454</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6993,7 +6993,7 @@
         <v>455</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7004,7 +7004,7 @@
         <v>456</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7015,7 +7015,7 @@
         <v>457</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7023,10 +7023,10 @@
         <v>1010028657</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7034,10 +7034,10 @@
         <v>1010028655</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7045,10 +7045,10 @@
         <v>145165</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7056,10 +7056,10 @@
         <v>51666</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7067,10 +7067,10 @@
         <v>1010080930</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7078,10 +7078,10 @@
         <v>161055</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7089,10 +7089,10 @@
         <v>1010050517</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7100,10 +7100,10 @@
         <v>1010084190</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7111,10 +7111,10 @@
         <v>1010084195</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7122,10 +7122,10 @@
         <v>1010001400</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7133,10 +7133,10 @@
         <v>1010008416</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7144,10 +7144,10 @@
         <v>1010018372</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7155,10 +7155,10 @@
         <v>1010018361</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7166,10 +7166,10 @@
         <v>1010055398</v>
       </c>
       <c r="B470" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7177,10 +7177,10 @@
         <v>422131</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7188,10 +7188,10 @@
         <v>1010084370</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7199,10 +7199,10 @@
         <v>422759</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7210,10 +7210,10 @@
         <v>120955</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7221,10 +7221,10 @@
         <v>1010000896</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7232,10 +7232,10 @@
         <v>1010084308</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7243,10 +7243,10 @@
         <v>1010084035</v>
       </c>
       <c r="B477" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7254,10 +7254,10 @@
         <v>1010062826</v>
       </c>
       <c r="B478" s="18" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7265,10 +7265,10 @@
         <v>1010002592</v>
       </c>
       <c r="B479" s="18" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7276,10 +7276,10 @@
         <v>1010001155</v>
       </c>
       <c r="B480" s="18" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7287,10 +7287,10 @@
         <v>1010001062</v>
       </c>
       <c r="B481" s="18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7298,10 +7298,10 @@
         <v>1010084328</v>
       </c>
       <c r="B482" s="18" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7309,10 +7309,10 @@
         <v>1010044502</v>
       </c>
       <c r="B483" s="18" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7320,10 +7320,10 @@
         <v>1010053692</v>
       </c>
       <c r="B484" s="18" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7331,10 +7331,10 @@
         <v>390742</v>
       </c>
       <c r="B485" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="C485" s="5" t="s">
         <v>491</v>
-      </c>
-      <c r="C485" s="5" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1758C6C7-39E7-436B-86AB-DAD646AC867C}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2E17758-BB04-42C7-8888-59074CD8A42F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="494">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -1516,6 +1516,9 @@
   </si>
   <si>
     <t>Borracharia</t>
+  </si>
+  <si>
+    <t>PARAFUSO 10X60 (CUICA)</t>
   </si>
 </sst>
 </file>
@@ -1596,7 +1599,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1660,11 +1663,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1716,6 +1745,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1731,6 +1766,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1996,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1195"/>
+  <dimension ref="A1:C1196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -4128,11 +4167,11 @@
       </c>
     </row>
     <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A194" s="8">
-        <v>1010003527</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>189</v>
+      <c r="A194" s="19">
+        <v>1010055707</v>
+      </c>
+      <c r="B194" s="20" t="s">
+        <v>493</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>480</v>
@@ -4140,21 +4179,21 @@
     </row>
     <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
+        <v>1010003527</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A196" s="8">
         <v>422027</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B196" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" s="4">
-        <v>1010011313</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="C196" s="5" t="s">
         <v>480</v>
@@ -4162,10 +4201,10 @@
     </row>
     <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
-        <v>27051</v>
+        <v>1010011313</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C197" s="5" t="s">
         <v>480</v>
@@ -4173,10 +4212,10 @@
     </row>
     <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
-        <v>1010011304</v>
+        <v>27051</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>480</v>
@@ -4184,10 +4223,10 @@
     </row>
     <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
-        <v>35659</v>
+        <v>1010011304</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>480</v>
@@ -4195,10 +4234,10 @@
     </row>
     <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
-        <v>1040077390</v>
+        <v>35659</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>480</v>
@@ -4206,10 +4245,10 @@
     </row>
     <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
-        <v>1010021542</v>
+        <v>1040077390</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C201" s="5" t="s">
         <v>480</v>
@@ -4217,10 +4256,10 @@
     </row>
     <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
-        <v>1010021733</v>
+        <v>1010021542</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>480</v>
@@ -4228,10 +4267,10 @@
     </row>
     <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
-        <v>1010011379</v>
+        <v>1010021733</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>480</v>
@@ -4239,10 +4278,10 @@
     </row>
     <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
-        <v>1010003279</v>
+        <v>1010011379</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C204" s="5" t="s">
         <v>480</v>
@@ -4250,10 +4289,10 @@
     </row>
     <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
-        <v>1010011380</v>
+        <v>1010003279</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>480</v>
@@ -4261,10 +4300,10 @@
     </row>
     <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
-        <v>351197</v>
+        <v>1010011380</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>480</v>
@@ -4272,10 +4311,10 @@
     </row>
     <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
-        <v>1010011286</v>
+        <v>351197</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>480</v>
@@ -4283,10 +4322,10 @@
     </row>
     <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
-        <v>2479</v>
+        <v>1010011286</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C208" s="5" t="s">
         <v>480</v>
@@ -4294,10 +4333,10 @@
     </row>
     <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
-        <v>1010011382</v>
+        <v>2479</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>480</v>
@@ -4305,10 +4344,10 @@
     </row>
     <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
-        <v>1010055703</v>
+        <v>1010011382</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>480</v>
@@ -4316,10 +4355,10 @@
     </row>
     <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
-        <v>4165</v>
+        <v>1010055703</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>480</v>
@@ -4327,10 +4366,10 @@
     </row>
     <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
-        <v>301626</v>
+        <v>4165</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>480</v>
@@ -4338,10 +4377,10 @@
     </row>
     <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
-        <v>429495</v>
+        <v>301626</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C213" s="5" t="s">
         <v>480</v>
@@ -4349,10 +4388,10 @@
     </row>
     <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
-        <v>162998</v>
+        <v>429495</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>480</v>
@@ -4360,10 +4399,10 @@
     </row>
     <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
-        <v>432657</v>
+        <v>162998</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>480</v>
@@ -4371,10 +4410,10 @@
     </row>
     <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
-        <v>1010021929</v>
+        <v>432657</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C216" s="5" t="s">
         <v>480</v>
@@ -4382,10 +4421,10 @@
     </row>
     <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
-        <v>428065</v>
+        <v>1010021929</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C217" s="5" t="s">
         <v>480</v>
@@ -4393,10 +4432,10 @@
     </row>
     <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
-        <v>1010003404</v>
+        <v>428065</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>480</v>
@@ -4404,10 +4443,10 @@
     </row>
     <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
-        <v>1010003322</v>
+        <v>1010003404</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C219" s="5" t="s">
         <v>480</v>
@@ -4415,10 +4454,10 @@
     </row>
     <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
-        <v>17738</v>
+        <v>1010003322</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C220" s="5" t="s">
         <v>480</v>
@@ -4426,10 +4465,10 @@
     </row>
     <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>1010085360</v>
+        <v>17738</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>480</v>
@@ -4437,10 +4476,10 @@
     </row>
     <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
-        <v>1040077391</v>
+        <v>1010085360</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C222" s="5" t="s">
         <v>480</v>
@@ -4448,10 +4487,10 @@
     </row>
     <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
-        <v>1010058624</v>
+        <v>1040077391</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C223" s="5" t="s">
         <v>480</v>
@@ -4459,10 +4498,10 @@
     </row>
     <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
-        <v>1010024661</v>
+        <v>1010058624</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>480</v>
@@ -4470,10 +4509,10 @@
     </row>
     <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
-        <v>1040019315</v>
+        <v>1010024661</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C225" s="5" t="s">
         <v>480</v>
@@ -4481,10 +4520,10 @@
     </row>
     <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
-        <v>1010021089</v>
+        <v>1040019315</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C226" s="5" t="s">
         <v>480</v>
@@ -4492,10 +4531,10 @@
     </row>
     <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
-        <v>1040017264</v>
+        <v>1010021089</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C227" s="5" t="s">
         <v>480</v>
@@ -4503,10 +4542,10 @@
     </row>
     <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
-        <v>1010051765</v>
+        <v>1040017264</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C228" s="5" t="s">
         <v>480</v>
@@ -4514,10 +4553,10 @@
     </row>
     <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
-        <v>1010035272</v>
+        <v>1010051765</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C229" s="5" t="s">
         <v>480</v>
@@ -4525,10 +4564,10 @@
     </row>
     <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
-        <v>1040077392</v>
+        <v>1010035272</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C230" s="5" t="s">
         <v>480</v>
@@ -4536,10 +4575,10 @@
     </row>
     <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
-        <v>1040077393</v>
+        <v>1040077392</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C231" s="5" t="s">
         <v>480</v>
@@ -4547,10 +4586,10 @@
     </row>
     <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
-        <v>1040077395</v>
+        <v>1040077393</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C232" s="5" t="s">
         <v>480</v>
@@ -4558,10 +4597,10 @@
     </row>
     <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
-        <v>1040077401</v>
+        <v>1040077395</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C233" s="5" t="s">
         <v>480</v>
@@ -4569,10 +4608,10 @@
     </row>
     <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
-        <v>27572</v>
+        <v>1040077401</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C234" s="5" t="s">
         <v>480</v>
@@ -4580,10 +4619,10 @@
     </row>
     <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
-        <v>18745</v>
+        <v>27572</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>480</v>
@@ -4591,10 +4630,10 @@
     </row>
     <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
-        <v>1040077396</v>
+        <v>18745</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C236" s="5" t="s">
         <v>480</v>
@@ -4602,10 +4641,10 @@
     </row>
     <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
-        <v>1010036546</v>
+        <v>1040077396</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C237" s="5" t="s">
         <v>480</v>
@@ -4613,10 +4652,10 @@
     </row>
     <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
-        <v>1010014049</v>
+        <v>1010036546</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C238" s="5" t="s">
         <v>480</v>
@@ -4624,10 +4663,10 @@
     </row>
     <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
-        <v>1010025148</v>
+        <v>1010014049</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C239" s="5" t="s">
         <v>480</v>
@@ -4635,10 +4674,10 @@
     </row>
     <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
-        <v>1040077394</v>
+        <v>1010025148</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C240" s="5" t="s">
         <v>480</v>
@@ -4646,10 +4685,10 @@
     </row>
     <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
-        <v>1040077400</v>
+        <v>1040077394</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C241" s="5" t="s">
         <v>480</v>
@@ -4657,10 +4696,10 @@
     </row>
     <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
-        <v>1040079329</v>
+        <v>1040077400</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C242" s="5" t="s">
         <v>480</v>
@@ -4668,10 +4707,10 @@
     </row>
     <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
-        <v>1040040957</v>
+        <v>1040079329</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C243" s="5" t="s">
         <v>480</v>
@@ -4679,10 +4718,10 @@
     </row>
     <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
-        <v>1040077398</v>
+        <v>1040040957</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C244" s="5" t="s">
         <v>480</v>
@@ -4690,10 +4729,10 @@
     </row>
     <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
-        <v>1010031545</v>
+        <v>1040077398</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C245" s="5" t="s">
         <v>480</v>
@@ -4701,10 +4740,10 @@
     </row>
     <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
-        <v>1010053128</v>
+        <v>1010031545</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C246" s="5" t="s">
         <v>480</v>
@@ -4712,10 +4751,10 @@
     </row>
     <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
-        <v>1010010599</v>
+        <v>1010053128</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C247" s="5" t="s">
         <v>480</v>
@@ -4723,10 +4762,10 @@
     </row>
     <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
-        <v>1010056064</v>
+        <v>1010010599</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C248" s="5" t="s">
         <v>480</v>
@@ -4734,10 +4773,10 @@
     </row>
     <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
-        <v>5389</v>
+        <v>1010056064</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C249" s="5" t="s">
         <v>480</v>
@@ -4745,10 +4784,10 @@
     </row>
     <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
-        <v>1010055969</v>
+        <v>5389</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C250" s="5" t="s">
         <v>480</v>
@@ -4756,10 +4795,10 @@
     </row>
     <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
-        <v>1010055970</v>
+        <v>1010055969</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C251" s="5" t="s">
         <v>480</v>
@@ -4767,32 +4806,32 @@
     </row>
     <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
+        <v>1010055970</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A253" s="4">
         <v>181395</v>
       </c>
-      <c r="B252" s="4" t="s">
+      <c r="B253" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A253" s="8">
+      <c r="C253" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A254" s="8">
         <v>1010055962</v>
       </c>
-      <c r="B253" s="4" t="s">
+      <c r="B254" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A254" s="4">
-        <v>1010003578</v>
-      </c>
-      <c r="B254" s="4" t="s">
-        <v>249</v>
       </c>
       <c r="C254" s="5" t="s">
         <v>480</v>
@@ -4800,10 +4839,10 @@
     </row>
     <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
-        <v>332891</v>
+        <v>1010003578</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C255" s="5" t="s">
         <v>480</v>
@@ -4811,10 +4850,10 @@
     </row>
     <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
-        <v>17727</v>
+        <v>332891</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C256" s="5" t="s">
         <v>480</v>
@@ -4822,10 +4861,10 @@
     </row>
     <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
-        <v>17918</v>
+        <v>17727</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C257" s="5" t="s">
         <v>480</v>
@@ -4833,10 +4872,10 @@
     </row>
     <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
-        <v>1010020554</v>
+        <v>17918</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C258" s="5" t="s">
         <v>480</v>
@@ -4844,10 +4883,10 @@
     </row>
     <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
-        <v>1040085949</v>
+        <v>1010020554</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C259" s="5" t="s">
         <v>480</v>
@@ -4855,10 +4894,10 @@
     </row>
     <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
-        <v>1010062938</v>
+        <v>1040085949</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C260" s="5" t="s">
         <v>480</v>
@@ -4866,10 +4905,10 @@
     </row>
     <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
-        <v>1010062086</v>
+        <v>1010062938</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C261" s="5" t="s">
         <v>480</v>
@@ -4877,10 +4916,10 @@
     </row>
     <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
-        <v>1010062087</v>
+        <v>1010062086</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C262" s="5" t="s">
         <v>480</v>
@@ -4888,21 +4927,21 @@
     </row>
     <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
+        <v>1010062087</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A264" s="4">
         <v>1040077373</v>
       </c>
-      <c r="B263" s="4" t="s">
+      <c r="B264" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A264" s="6">
-        <v>1040077372</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="C264" s="5" t="s">
         <v>480</v>
@@ -4910,10 +4949,10 @@
     </row>
     <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
-        <v>1040097154</v>
+        <v>1040077372</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C265" s="5" t="s">
         <v>480</v>
@@ -4921,21 +4960,21 @@
     </row>
     <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
+        <v>1040097154</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A267" s="6">
         <v>1010042579</v>
       </c>
-      <c r="B266" s="6" t="s">
+      <c r="B267" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="C266" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A267" s="4">
-        <v>1010029427</v>
-      </c>
-      <c r="B267" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="C267" s="5" t="s">
         <v>480</v>
@@ -4943,10 +4982,10 @@
     </row>
     <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
-        <v>133108</v>
+        <v>1010029427</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C268" s="5" t="s">
         <v>480</v>
@@ -4954,10 +4993,10 @@
     </row>
     <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
-        <v>269427</v>
+        <v>133108</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C269" s="5" t="s">
         <v>480</v>
@@ -4965,10 +5004,10 @@
     </row>
     <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
-        <v>298227</v>
+        <v>269427</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C270" s="5" t="s">
         <v>480</v>
@@ -4976,10 +5015,10 @@
     </row>
     <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
-        <v>1010062285</v>
+        <v>298227</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C271" s="5" t="s">
         <v>480</v>
@@ -4987,10 +5026,10 @@
     </row>
     <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
-        <v>1010058052</v>
+        <v>1010062285</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C272" s="5" t="s">
         <v>480</v>
@@ -4998,21 +5037,21 @@
     </row>
     <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
+        <v>1010058052</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A274" s="4">
         <v>1010050033</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B274" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="C273" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A274" s="9">
-        <v>1040098869</v>
-      </c>
-      <c r="B274" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="C274" s="5" t="s">
         <v>480</v>
@@ -5020,10 +5059,10 @@
     </row>
     <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="9">
-        <v>1010056523</v>
+        <v>1040098869</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C275" s="5" t="s">
         <v>480</v>
@@ -5031,21 +5070,21 @@
     </row>
     <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="9">
+        <v>1010056523</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A277" s="9">
         <v>1010062045</v>
       </c>
-      <c r="B276" s="4" t="s">
+      <c r="B277" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A277" s="4">
-        <v>1040097575</v>
-      </c>
-      <c r="B277" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="C277" s="5" t="s">
         <v>480</v>
@@ -5053,10 +5092,10 @@
     </row>
     <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
-        <v>1040098437</v>
+        <v>1040097575</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C278" s="5" t="s">
         <v>480</v>
@@ -5064,10 +5103,10 @@
     </row>
     <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
-        <v>1010040346</v>
+        <v>1040098437</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C279" s="5" t="s">
         <v>480</v>
@@ -5075,10 +5114,10 @@
     </row>
     <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
-        <v>1010021543</v>
+        <v>1010040346</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C280" s="5" t="s">
         <v>480</v>
@@ -5086,10 +5125,10 @@
     </row>
     <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
-        <v>1040077397</v>
+        <v>1010021543</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>480</v>
@@ -5097,10 +5136,10 @@
     </row>
     <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
-        <v>1040094213</v>
+        <v>1040077397</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>480</v>
@@ -5108,10 +5147,10 @@
     </row>
     <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
-        <v>1010085326</v>
+        <v>1040094213</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C283" s="5" t="s">
         <v>480</v>
@@ -5119,10 +5158,10 @@
     </row>
     <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
-        <v>1010042564</v>
+        <v>1010085326</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C284" s="5" t="s">
         <v>480</v>
@@ -5130,10 +5169,10 @@
     </row>
     <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
-        <v>1010042688</v>
+        <v>1010042564</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C285" s="5" t="s">
         <v>480</v>
@@ -5141,10 +5180,10 @@
     </row>
     <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
-        <v>1010040133</v>
+        <v>1010042688</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C286" s="5" t="s">
         <v>480</v>
@@ -5152,10 +5191,10 @@
     </row>
     <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
-        <v>1010039879</v>
+        <v>1010040133</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C287" s="5" t="s">
         <v>480</v>
@@ -5163,10 +5202,10 @@
     </row>
     <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
-        <v>62608</v>
+        <v>1010039879</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C288" s="5" t="s">
         <v>480</v>
@@ -5174,10 +5213,10 @@
     </row>
     <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
-        <v>1040098603</v>
+        <v>62608</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C289" s="5" t="s">
         <v>480</v>
@@ -5185,10 +5224,10 @@
     </row>
     <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
-        <v>1040017266</v>
+        <v>1040098603</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C290" s="5" t="s">
         <v>480</v>
@@ -5196,10 +5235,10 @@
     </row>
     <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
-        <v>1010063326</v>
+        <v>1040017266</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C291" s="5" t="s">
         <v>480</v>
@@ -5207,10 +5246,10 @@
     </row>
     <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
-        <v>1010050574</v>
+        <v>1010063326</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C292" s="5" t="s">
         <v>480</v>
@@ -5218,10 +5257,10 @@
     </row>
     <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
-        <v>1040087856</v>
+        <v>1010050574</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C293" s="5" t="s">
         <v>480</v>
@@ -5229,10 +5268,10 @@
     </row>
     <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
-        <v>1040019838</v>
+        <v>1040087856</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C294" s="5" t="s">
         <v>480</v>
@@ -5240,10 +5279,10 @@
     </row>
     <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
-        <v>1010042882</v>
+        <v>1040019838</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C295" s="5" t="s">
         <v>480</v>
@@ -5251,10 +5290,10 @@
     </row>
     <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
-        <v>1010042873</v>
+        <v>1010042882</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C296" s="5" t="s">
         <v>480</v>
@@ -5262,10 +5301,10 @@
     </row>
     <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
-        <v>1010059549</v>
+        <v>1010042873</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C297" s="5" t="s">
         <v>480</v>
@@ -5273,10 +5312,10 @@
     </row>
     <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
-        <v>1010020552</v>
+        <v>1010059549</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C298" s="5" t="s">
         <v>480</v>
@@ -5284,10 +5323,10 @@
     </row>
     <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
-        <v>1040078895</v>
+        <v>1010020552</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C299" s="5" t="s">
         <v>480</v>
@@ -5295,10 +5334,10 @@
     </row>
     <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
-        <v>1040024309</v>
+        <v>1040078895</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C300" s="5" t="s">
         <v>480</v>
@@ -5306,10 +5345,10 @@
     </row>
     <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
-        <v>1040024323</v>
+        <v>1040024309</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C301" s="5" t="s">
         <v>480</v>
@@ -5317,10 +5356,10 @@
     </row>
     <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
-        <v>1040024322</v>
+        <v>1040024323</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C302" s="5" t="s">
         <v>480</v>
@@ -5328,10 +5367,10 @@
     </row>
     <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
-        <v>1040024314</v>
+        <v>1040024322</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C303" s="5" t="s">
         <v>480</v>
@@ -5339,10 +5378,10 @@
     </row>
     <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
-        <v>1010059685</v>
+        <v>1040024314</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C304" s="5" t="s">
         <v>480</v>
@@ -5350,10 +5389,10 @@
     </row>
     <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
-        <v>1010059687</v>
+        <v>1010059685</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C305" s="5" t="s">
         <v>480</v>
@@ -5361,10 +5400,10 @@
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
-        <v>1010077469</v>
+        <v>1010059687</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C306" s="5" t="s">
         <v>480</v>
@@ -5372,32 +5411,32 @@
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
+        <v>1010077469</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A308" s="4">
         <v>1010077470</v>
       </c>
-      <c r="B307" s="4" t="s">
+      <c r="B308" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A308" s="4" t="s">
+      <c r="C308" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B308" s="4" t="s">
+      <c r="B309" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A309" s="4">
-        <v>1010084108</v>
-      </c>
-      <c r="B309" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="C309" s="5" t="s">
         <v>480</v>
@@ -5405,10 +5444,10 @@
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
-        <v>1040043537</v>
+        <v>1010084108</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C310" s="5" t="s">
         <v>480</v>
@@ -5416,10 +5455,10 @@
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
-        <v>1010046401</v>
+        <v>1040043537</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C311" s="5" t="s">
         <v>480</v>
@@ -5427,10 +5466,10 @@
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
-        <v>1010062007</v>
+        <v>1010046401</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C312" s="5" t="s">
         <v>480</v>
@@ -5438,10 +5477,10 @@
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
-        <v>1010051284</v>
+        <v>1010062007</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>480</v>
@@ -5449,10 +5488,10 @@
     </row>
     <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
-        <v>1010027788</v>
+        <v>1010051284</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C314" s="5" t="s">
         <v>480</v>
@@ -5460,10 +5499,10 @@
     </row>
     <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
-        <v>1010027786</v>
+        <v>1010027788</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>480</v>
@@ -5471,32 +5510,32 @@
     </row>
     <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
+        <v>1010027786</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A317" s="4">
         <v>1010026889</v>
       </c>
-      <c r="B316" s="4" t="s">
+      <c r="B317" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C316" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A317" s="6">
+      <c r="C317" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A318" s="6">
         <v>1010042358</v>
       </c>
-      <c r="B317" s="4" t="s">
+      <c r="B318" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="C317" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A318" s="4">
-        <v>1040023848</v>
-      </c>
-      <c r="B318" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="C318" s="5" t="s">
         <v>480</v>
@@ -5504,10 +5543,10 @@
     </row>
     <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
-        <v>1010042341</v>
+        <v>1040023848</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>480</v>
@@ -5515,10 +5554,10 @@
     </row>
     <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
-        <v>1040023858</v>
+        <v>1010042341</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C320" s="5" t="s">
         <v>480</v>
@@ -5526,10 +5565,10 @@
     </row>
     <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
-        <v>1040023843</v>
+        <v>1040023858</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>480</v>
@@ -5537,10 +5576,10 @@
     </row>
     <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
-        <v>1040077411</v>
+        <v>1040023843</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>480</v>
@@ -5548,10 +5587,10 @@
     </row>
     <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
-        <v>1040077410</v>
+        <v>1040077411</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>480</v>
@@ -5559,10 +5598,10 @@
     </row>
     <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
-        <v>1010062008</v>
+        <v>1040077410</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C324" s="5" t="s">
         <v>480</v>
@@ -5570,10 +5609,10 @@
     </row>
     <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
-        <v>1040040960</v>
+        <v>1010062008</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>480</v>
@@ -5581,10 +5620,10 @@
     </row>
     <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
-        <v>409578</v>
+        <v>1040040960</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>480</v>
@@ -5592,10 +5631,10 @@
     </row>
     <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
-        <v>1040077360</v>
+        <v>409578</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C327" s="5" t="s">
         <v>480</v>
@@ -5603,10 +5642,10 @@
     </row>
     <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
-        <v>1010064470</v>
+        <v>1040077360</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>480</v>
@@ -5614,10 +5653,10 @@
     </row>
     <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
-        <v>1010021991</v>
+        <v>1010064470</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>480</v>
@@ -5625,10 +5664,10 @@
     </row>
     <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
-        <v>1010021960</v>
+        <v>1010021991</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C330" s="5" t="s">
         <v>480</v>
@@ -5636,10 +5675,10 @@
     </row>
     <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
-        <v>1010031545</v>
+        <v>1010021960</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C331" s="5" t="s">
         <v>480</v>
@@ -5647,10 +5686,10 @@
     </row>
     <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
-        <v>1010022590</v>
+        <v>1010031545</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>480</v>
@@ -5658,30 +5697,30 @@
     </row>
     <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
+        <v>1010022590</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A334" s="4">
         <v>1040098643</v>
       </c>
-      <c r="B333" s="4" t="s">
+      <c r="B334" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C333" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A334" s="4"/>
-      <c r="B334" s="4" t="s">
+      <c r="C334" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A335" s="4"/>
+      <c r="B335" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="C334" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A335" s="4">
-        <v>1010046550</v>
-      </c>
-      <c r="B335" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="C335" s="5" t="s">
         <v>480</v>
@@ -5689,10 +5728,10 @@
     </row>
     <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
-        <v>1010046402</v>
+        <v>1010046550</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>480</v>
@@ -5700,10 +5739,10 @@
     </row>
     <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
-        <v>1010060291</v>
+        <v>1010046402</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C337" s="5" t="s">
         <v>480</v>
@@ -5711,10 +5750,10 @@
     </row>
     <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
-        <v>1010050920</v>
+        <v>1010060291</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C338" s="5" t="s">
         <v>480</v>
@@ -5722,10 +5761,10 @@
     </row>
     <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
-        <v>1040077412</v>
+        <v>1010050920</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C339" s="5" t="s">
         <v>480</v>
@@ -5733,10 +5772,10 @@
     </row>
     <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
-        <v>1010042609</v>
+        <v>1040077412</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C340" s="5" t="s">
         <v>480</v>
@@ -5744,10 +5783,10 @@
     </row>
     <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
-        <v>417701</v>
+        <v>1010042609</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C341" s="5" t="s">
         <v>480</v>
@@ -5755,32 +5794,32 @@
     </row>
     <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
+        <v>417701</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A343" s="4">
         <v>399384</v>
       </c>
-      <c r="B342" s="4" t="s">
+      <c r="B343" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C342" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A343" s="10">
+      <c r="C343" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A344" s="10">
         <v>1010024086</v>
       </c>
-      <c r="B343" s="10" t="s">
+      <c r="B344" s="10" t="s">
         <v>429</v>
-      </c>
-      <c r="C343" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A344" s="4">
-        <v>1040077345</v>
-      </c>
-      <c r="B344" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="C344" s="5" t="s">
         <v>480</v>
@@ -5788,10 +5827,10 @@
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
-        <v>1010084315</v>
+        <v>1040077345</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C345" s="5" t="s">
         <v>480</v>
@@ -5799,10 +5838,10 @@
     </row>
     <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
-        <v>399253</v>
+        <v>1010084315</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C346" s="5" t="s">
         <v>480</v>
@@ -5810,32 +5849,32 @@
     </row>
     <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
+        <v>399253</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A348" s="4">
         <v>1010084317</v>
       </c>
-      <c r="B347" s="4" t="s">
+      <c r="B348" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C347" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A348" s="11">
+      <c r="C348" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A349" s="11">
         <v>1010085369</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="B349" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="C348" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A349" s="4">
-        <v>1010085370</v>
-      </c>
-      <c r="B349" s="4" t="s">
-        <v>344</v>
       </c>
       <c r="C349" s="5" t="s">
         <v>480</v>
@@ -5843,10 +5882,10 @@
     </row>
     <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
-        <v>1010085204</v>
+        <v>1010085370</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C350" s="5" t="s">
         <v>480</v>
@@ -5854,10 +5893,10 @@
     </row>
     <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
-        <v>1010003966</v>
+        <v>1010085204</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C351" s="5" t="s">
         <v>480</v>
@@ -5865,10 +5904,10 @@
     </row>
     <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
-        <v>1010003967</v>
+        <v>1010003966</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C352" s="5" t="s">
         <v>480</v>
@@ -5876,10 +5915,10 @@
     </row>
     <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
-        <v>65219</v>
+        <v>1010003967</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C353" s="5" t="s">
         <v>480</v>
@@ -5887,10 +5926,10 @@
     </row>
     <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
-        <v>10168</v>
+        <v>65219</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C354" s="5" t="s">
         <v>480</v>
@@ -5898,10 +5937,10 @@
     </row>
     <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
-        <v>1010083792</v>
+        <v>10168</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C355" s="5" t="s">
         <v>480</v>
@@ -5909,10 +5948,10 @@
     </row>
     <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
-        <v>1040077414</v>
+        <v>1010083792</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C356" s="5" t="s">
         <v>480</v>
@@ -5920,10 +5959,10 @@
     </row>
     <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
-        <v>1010018482</v>
+        <v>1040077414</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C357" s="5" t="s">
         <v>480</v>
@@ -5931,10 +5970,10 @@
     </row>
     <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
-        <v>1010084320</v>
+        <v>1010018482</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C358" s="5" t="s">
         <v>480</v>
@@ -5942,10 +5981,10 @@
     </row>
     <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
-        <v>1010084532</v>
+        <v>1010084320</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C359" s="5" t="s">
         <v>480</v>
@@ -5953,10 +5992,10 @@
     </row>
     <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
-        <v>1010027285</v>
+        <v>1010084532</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C360" s="5" t="s">
         <v>480</v>
@@ -5964,10 +6003,10 @@
     </row>
     <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
-        <v>1040077413</v>
+        <v>1010027285</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C361" s="5" t="s">
         <v>480</v>
@@ -5975,10 +6014,10 @@
     </row>
     <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
-        <v>1010085376</v>
+        <v>1040077413</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C362" s="5" t="s">
         <v>480</v>
@@ -5986,10 +6025,10 @@
     </row>
     <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
-        <v>1010022819</v>
+        <v>1010085376</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C363" s="5" t="s">
         <v>480</v>
@@ -5997,10 +6036,10 @@
     </row>
     <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
-        <v>1010052853</v>
+        <v>1010022819</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C364" s="5" t="s">
         <v>480</v>
@@ -6008,10 +6047,10 @@
     </row>
     <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
-        <v>1010084377</v>
+        <v>1010052853</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C365" s="5" t="s">
         <v>480</v>
@@ -6019,21 +6058,21 @@
     </row>
     <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
-        <v>1010008578</v>
+        <v>1010084377</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
-        <v>1010031694</v>
+        <v>1010008578</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C367" s="5" t="s">
         <v>481</v>
@@ -6041,10 +6080,10 @@
     </row>
     <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
-        <v>1010051997</v>
+        <v>1010031694</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C368" s="5" t="s">
         <v>481</v>
@@ -6052,10 +6091,10 @@
     </row>
     <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
-        <v>1010022601</v>
+        <v>1010051997</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C369" s="5" t="s">
         <v>481</v>
@@ -6063,10 +6102,10 @@
     </row>
     <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
-        <v>1010054278</v>
+        <v>1010022601</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C370" s="5" t="s">
         <v>481</v>
@@ -6074,10 +6113,10 @@
     </row>
     <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
-        <v>1010083462</v>
+        <v>1010054278</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C371" s="5" t="s">
         <v>481</v>
@@ -6085,10 +6124,10 @@
     </row>
     <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
-        <v>1010027772</v>
+        <v>1010083462</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C372" s="5" t="s">
         <v>481</v>
@@ -6096,10 +6135,10 @@
     </row>
     <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
-        <v>1010084144</v>
+        <v>1010027772</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C373" s="5" t="s">
         <v>481</v>
@@ -6107,21 +6146,21 @@
     </row>
     <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="4">
-        <v>214055</v>
+        <v>1010084144</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C374" s="5" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A375" s="8">
-        <v>1010021956</v>
+      <c r="A375" s="4">
+        <v>214055</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C375" s="5" t="s">
         <v>481</v>
@@ -6129,21 +6168,21 @@
     </row>
     <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" s="8">
-        <v>1010026464</v>
+        <v>1010021956</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C376" s="5" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A377" s="4">
-        <v>1010021957</v>
+      <c r="A377" s="8">
+        <v>1010026464</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C377" s="5" t="s">
         <v>481</v>
@@ -6151,10 +6190,10 @@
     </row>
     <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="4">
-        <v>1010026462</v>
+        <v>1010021957</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C378" s="5" t="s">
         <v>481</v>
@@ -6162,10 +6201,10 @@
     </row>
     <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
-        <v>1010026551</v>
+        <v>1010026462</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C379" s="5" t="s">
         <v>481</v>
@@ -6173,10 +6212,10 @@
     </row>
     <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
-        <v>1010042554</v>
+        <v>1010026551</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C380" s="5" t="s">
         <v>481</v>
@@ -6184,10 +6223,10 @@
     </row>
     <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
-        <v>1010039904</v>
+        <v>1010042554</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C381" s="5" t="s">
         <v>481</v>
@@ -6195,10 +6234,10 @@
     </row>
     <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="4">
-        <v>1010060205</v>
+        <v>1010039904</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C382" s="5" t="s">
         <v>481</v>
@@ -6206,10 +6245,10 @@
     </row>
     <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
-        <v>1010060206</v>
+        <v>1010060205</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C383" s="5" t="s">
         <v>481</v>
@@ -6217,10 +6256,10 @@
     </row>
     <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="4">
-        <v>1010077431</v>
+        <v>1010060206</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C384" s="5" t="s">
         <v>481</v>
@@ -6228,10 +6267,10 @@
     </row>
     <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
-        <v>1010077503</v>
+        <v>1010077431</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C385" s="5" t="s">
         <v>481</v>
@@ -6239,10 +6278,10 @@
     </row>
     <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
-        <v>1010084187</v>
+        <v>1010077503</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C386" s="5" t="s">
         <v>481</v>
@@ -6250,10 +6289,10 @@
     </row>
     <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
-        <v>1010080958</v>
+        <v>1010084187</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C387" s="5" t="s">
         <v>481</v>
@@ -6261,10 +6300,10 @@
     </row>
     <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
-        <v>1010026032</v>
+        <v>1010080958</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C388" s="5" t="s">
         <v>481</v>
@@ -6272,10 +6311,10 @@
     </row>
     <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
-        <v>1010085384</v>
+        <v>1010026032</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C389" s="5" t="s">
         <v>481</v>
@@ -6283,10 +6322,10 @@
     </row>
     <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
-        <v>1010006347</v>
+        <v>1010085384</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C390" s="5" t="s">
         <v>481</v>
@@ -6294,10 +6333,10 @@
     </row>
     <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
-        <v>1010085179</v>
+        <v>1010006347</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C391" s="5" t="s">
         <v>481</v>
@@ -6305,10 +6344,10 @@
     </row>
     <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="4">
-        <v>1010024158</v>
+        <v>1010085179</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C392" s="5" t="s">
         <v>481</v>
@@ -6316,10 +6355,10 @@
     </row>
     <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
-        <v>1010024131</v>
+        <v>1010024158</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C393" s="5" t="s">
         <v>481</v>
@@ -6327,10 +6366,10 @@
     </row>
     <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
-        <v>1010007160</v>
+        <v>1010024131</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C394" s="5" t="s">
         <v>481</v>
@@ -6338,10 +6377,10 @@
     </row>
     <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
-        <v>1010023642</v>
+        <v>1010007160</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C395" s="5" t="s">
         <v>481</v>
@@ -6349,10 +6388,10 @@
     </row>
     <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
-        <v>1010007193</v>
-      </c>
-      <c r="B396" s="6" t="s">
-        <v>391</v>
+        <v>1010023642</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>390</v>
       </c>
       <c r="C396" s="5" t="s">
         <v>481</v>
@@ -6360,10 +6399,10 @@
     </row>
     <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
-        <v>1010042637</v>
-      </c>
-      <c r="B397" s="4" t="s">
-        <v>392</v>
+        <v>1010007193</v>
+      </c>
+      <c r="B397" s="6" t="s">
+        <v>391</v>
       </c>
       <c r="C397" s="5" t="s">
         <v>481</v>
@@ -6371,10 +6410,10 @@
     </row>
     <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
-        <v>1040075323</v>
+        <v>1010042637</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C398" s="5" t="s">
         <v>481</v>
@@ -6382,10 +6421,10 @@
     </row>
     <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="4">
-        <v>1040075324</v>
+        <v>1040075323</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C399" s="5" t="s">
         <v>481</v>
@@ -6393,10 +6432,10 @@
     </row>
     <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="4">
-        <v>1040083312</v>
+        <v>1040075324</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C400" s="5" t="s">
         <v>481</v>
@@ -6404,10 +6443,10 @@
     </row>
     <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
-        <v>1040077661</v>
+        <v>1040083312</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C401" s="5" t="s">
         <v>481</v>
@@ -6415,10 +6454,10 @@
     </row>
     <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="4">
-        <v>1010085180</v>
-      </c>
-      <c r="B402" s="12" t="s">
-        <v>397</v>
+        <v>1040077661</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="C402" s="5" t="s">
         <v>481</v>
@@ -6426,10 +6465,10 @@
     </row>
     <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
-        <v>1040017489</v>
-      </c>
-      <c r="B403" s="4" t="s">
-        <v>398</v>
+        <v>1010085180</v>
+      </c>
+      <c r="B403" s="12" t="s">
+        <v>397</v>
       </c>
       <c r="C403" s="5" t="s">
         <v>481</v>
@@ -6437,10 +6476,10 @@
     </row>
     <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
-        <v>1010085181</v>
+        <v>1040017489</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C404" s="5" t="s">
         <v>481</v>
@@ -6448,10 +6487,10 @@
     </row>
     <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
-        <v>400175</v>
+        <v>1010085181</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C405" s="5" t="s">
         <v>481</v>
@@ -6459,10 +6498,10 @@
     </row>
     <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
-        <v>1040017505</v>
+        <v>400175</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C406" s="5" t="s">
         <v>481</v>
@@ -6470,10 +6509,10 @@
     </row>
     <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
-        <v>1040017503</v>
+        <v>1040017505</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C407" s="5" t="s">
         <v>481</v>
@@ -6481,10 +6520,10 @@
     </row>
     <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
-        <v>1010046445</v>
+        <v>1040017503</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C408" s="5" t="s">
         <v>481</v>
@@ -6492,10 +6531,10 @@
     </row>
     <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
-        <v>1010021033</v>
+        <v>1010046445</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C409" s="5" t="s">
         <v>481</v>
@@ -6503,10 +6542,10 @@
     </row>
     <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="4">
-        <v>1010057142</v>
+        <v>1010021033</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C410" s="5" t="s">
         <v>481</v>
@@ -6514,10 +6553,10 @@
     </row>
     <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
-        <v>1010016356</v>
+        <v>1010057142</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C411" s="5" t="s">
         <v>481</v>
@@ -6525,10 +6564,10 @@
     </row>
     <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
-        <v>1010084363</v>
+        <v>1010016356</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C412" s="5" t="s">
         <v>481</v>
@@ -6536,10 +6575,10 @@
     </row>
     <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
-        <v>1010052021</v>
+        <v>1010084363</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C413" s="5" t="s">
         <v>481</v>
@@ -6547,10 +6586,10 @@
     </row>
     <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
-        <v>1040091721</v>
+        <v>1010052021</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C414" s="5" t="s">
         <v>481</v>
@@ -6558,10 +6597,10 @@
     </row>
     <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
-        <v>1010062022</v>
+        <v>1040091721</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C415" s="5" t="s">
         <v>481</v>
@@ -6569,10 +6608,10 @@
     </row>
     <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
-        <v>18336</v>
+        <v>1010062022</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C416" s="5" t="s">
         <v>481</v>
@@ -6580,10 +6619,10 @@
     </row>
     <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
-        <v>229205</v>
+        <v>18336</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C417" s="5" t="s">
         <v>481</v>
@@ -6591,10 +6630,10 @@
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
-        <v>60671</v>
+        <v>229205</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C418" s="5" t="s">
         <v>481</v>
@@ -6602,10 +6641,10 @@
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
-        <v>1010059726</v>
+        <v>60671</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C419" s="5" t="s">
         <v>481</v>
@@ -6613,10 +6652,10 @@
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="4">
-        <v>1010008144</v>
+        <v>1010059726</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C420" s="5" t="s">
         <v>481</v>
@@ -6624,10 +6663,10 @@
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
-        <v>1010007244</v>
+        <v>1010008144</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C421" s="5" t="s">
         <v>481</v>
@@ -6635,10 +6674,10 @@
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="4">
-        <v>1010006827</v>
+        <v>1010007244</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C422" s="5" t="s">
         <v>481</v>
@@ -6646,10 +6685,10 @@
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
-        <v>1040075426</v>
+        <v>1010006827</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C423" s="5" t="s">
         <v>481</v>
@@ -6657,10 +6696,10 @@
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="4">
-        <v>1040075427</v>
+        <v>1040075426</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C424" s="5" t="s">
         <v>481</v>
@@ -6668,10 +6707,10 @@
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
-        <v>1010084313</v>
+        <v>1040075427</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C425" s="5" t="s">
         <v>481</v>
@@ -6679,10 +6718,10 @@
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
-        <v>403459</v>
+        <v>1010084313</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C426" s="5" t="s">
         <v>481</v>
@@ -6690,10 +6729,10 @@
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
-        <v>1010044828</v>
+        <v>403459</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C427" s="5" t="s">
         <v>481</v>
@@ -6701,10 +6740,10 @@
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
-        <v>1010026973</v>
+        <v>1010044828</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C428" s="5" t="s">
         <v>481</v>
@@ -6712,32 +6751,32 @@
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
-        <v>1040017204</v>
+        <v>1010026973</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C429" s="5" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A430" s="6">
+      <c r="A430" s="4">
+        <v>1040017204</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A431" s="6">
         <v>1010022119</v>
       </c>
-      <c r="B430" s="6" t="s">
+      <c r="B431" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="C430" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="4">
-        <v>1010034964</v>
-      </c>
-      <c r="B431" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="C431" s="5" t="s">
         <v>492</v>
@@ -6745,10 +6784,10 @@
     </row>
     <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
-        <v>1010058709</v>
+        <v>1010034964</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C432" s="5" t="s">
         <v>492</v>
@@ -6756,10 +6795,10 @@
     </row>
     <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
-        <v>1010025711</v>
+        <v>1010058709</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C433" s="5" t="s">
         <v>492</v>
@@ -6767,10 +6806,10 @@
     </row>
     <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
-        <v>1010059684</v>
+        <v>1010025711</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C434" s="5" t="s">
         <v>492</v>
@@ -6778,10 +6817,10 @@
     </row>
     <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="4">
-        <v>427341</v>
+        <v>1010059684</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C435" s="5" t="s">
         <v>492</v>
@@ -6789,10 +6828,10 @@
     </row>
     <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="4">
-        <v>1010085279</v>
+        <v>427341</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C436" s="5" t="s">
         <v>492</v>
@@ -6800,10 +6839,10 @@
     </row>
     <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
-        <v>1010022588</v>
+        <v>1010085279</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C437" s="5" t="s">
         <v>492</v>
@@ -6811,10 +6850,10 @@
     </row>
     <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="4">
-        <v>1010026864</v>
+        <v>1010022588</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C438" s="5" t="s">
         <v>492</v>
@@ -6822,10 +6861,10 @@
     </row>
     <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
-        <v>1010030946</v>
+        <v>1010026864</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C439" s="5" t="s">
         <v>492</v>
@@ -6833,10 +6872,10 @@
     </row>
     <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="4">
-        <v>1010022589</v>
+        <v>1010030946</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C440" s="5" t="s">
         <v>492</v>
@@ -6844,10 +6883,10 @@
     </row>
     <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="4">
-        <v>1040090143</v>
+        <v>1010022589</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C441" s="5" t="s">
         <v>492</v>
@@ -6855,10 +6894,10 @@
     </row>
     <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="4">
-        <v>1040090138</v>
+        <v>1040090143</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C442" s="5" t="s">
         <v>492</v>
@@ -6866,10 +6905,10 @@
     </row>
     <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="4">
-        <v>1030001314</v>
+        <v>1040090138</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C443" s="5" t="s">
         <v>492</v>
@@ -6877,10 +6916,10 @@
     </row>
     <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="4">
-        <v>1010052319</v>
+        <v>1030001314</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C444" s="5" t="s">
         <v>492</v>
@@ -6888,10 +6927,10 @@
     </row>
     <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="4">
-        <v>1010052320</v>
+        <v>1010052319</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C445" s="5" t="s">
         <v>492</v>
@@ -6899,10 +6938,10 @@
     </row>
     <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="4">
-        <v>1030000370</v>
+        <v>1010052320</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C446" s="5" t="s">
         <v>492</v>
@@ -6910,10 +6949,10 @@
     </row>
     <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="4">
-        <v>1030000366</v>
+        <v>1030000370</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C447" s="5" t="s">
         <v>492</v>
@@ -6921,10 +6960,10 @@
     </row>
     <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="4">
-        <v>1030000368</v>
+        <v>1030000366</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C448" s="5" t="s">
         <v>492</v>
@@ -6932,10 +6971,10 @@
     </row>
     <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="4">
-        <v>1030000369</v>
+        <v>1030000368</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C449" s="5" t="s">
         <v>492</v>
@@ -6943,10 +6982,10 @@
     </row>
     <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="4">
-        <v>1030000489</v>
+        <v>1030000369</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C450" s="5" t="s">
         <v>492</v>
@@ -6954,10 +6993,10 @@
     </row>
     <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
-        <v>1030000490</v>
+        <v>1030000489</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C451" s="5" t="s">
         <v>492</v>
@@ -6965,10 +7004,10 @@
     </row>
     <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="4">
-        <v>1030000821</v>
+        <v>1030000490</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C452" s="5" t="s">
         <v>492</v>
@@ -6976,10 +7015,10 @@
     </row>
     <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
-        <v>1030000511</v>
+        <v>1030000821</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C453" s="5" t="s">
         <v>492</v>
@@ -6987,10 +7026,10 @@
     </row>
     <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="4">
-        <v>1010084279</v>
+        <v>1030000511</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C454" s="5" t="s">
         <v>492</v>
@@ -6998,10 +7037,10 @@
     </row>
     <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="4">
-        <v>1010004281</v>
+        <v>1010084279</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C455" s="5" t="s">
         <v>492</v>
@@ -7009,10 +7048,10 @@
     </row>
     <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="4">
-        <v>1010022118</v>
+        <v>1010004281</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C456" s="5" t="s">
         <v>492</v>
@@ -7020,21 +7059,21 @@
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
+        <v>1010022118</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A458" s="4">
         <v>1010028657</v>
       </c>
-      <c r="B457" s="4" t="s">
+      <c r="B458" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="C457" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="8">
-        <v>1010028655</v>
-      </c>
-      <c r="B458" s="4" t="s">
-        <v>459</v>
       </c>
       <c r="C458" s="5" t="s">
         <v>482</v>
@@ -7042,43 +7081,43 @@
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="8">
-        <v>145165</v>
+        <v>1010028655</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C459" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="4">
-        <v>51666</v>
+      <c r="A460" s="8">
+        <v>145165</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C460" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="8">
-        <v>1010080930</v>
+      <c r="A461" s="4">
+        <v>51666</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C461" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="4">
-        <v>161055</v>
+      <c r="A462" s="8">
+        <v>1010080930</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C462" s="5" t="s">
         <v>482</v>
@@ -7086,10 +7125,10 @@
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
-        <v>1010050517</v>
+        <v>161055</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C463" s="5" t="s">
         <v>482</v>
@@ -7097,10 +7136,10 @@
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
-        <v>1010084190</v>
+        <v>1010050517</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C464" s="5" t="s">
         <v>482</v>
@@ -7108,10 +7147,10 @@
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
-        <v>1010084195</v>
+        <v>1010084190</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C465" s="5" t="s">
         <v>482</v>
@@ -7119,32 +7158,32 @@
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
-        <v>1010001400</v>
+        <v>1010084195</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C466" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="8">
-        <v>1010008416</v>
+      <c r="A467" s="4">
+        <v>1010001400</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C467" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="13">
-        <v>1010018372</v>
+      <c r="A468" s="8">
+        <v>1010008416</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C468" s="5" t="s">
         <v>482</v>
@@ -7152,21 +7191,21 @@
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="13">
-        <v>1010018361</v>
+        <v>1010018372</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C469" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="4">
-        <v>1010055398</v>
-      </c>
-      <c r="B470" s="8" t="s">
-        <v>471</v>
+      <c r="A470" s="13">
+        <v>1010018361</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>470</v>
       </c>
       <c r="C470" s="5" t="s">
         <v>482</v>
@@ -7174,10 +7213,10 @@
     </row>
     <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
-        <v>422131</v>
-      </c>
-      <c r="B471" s="4" t="s">
-        <v>472</v>
+        <v>1010055398</v>
+      </c>
+      <c r="B471" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="C471" s="5" t="s">
         <v>482</v>
@@ -7185,10 +7224,10 @@
     </row>
     <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
-        <v>1010084370</v>
+        <v>422131</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C472" s="5" t="s">
         <v>482</v>
@@ -7196,10 +7235,10 @@
     </row>
     <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
-        <v>422759</v>
+        <v>1010084370</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C473" s="5" t="s">
         <v>482</v>
@@ -7207,10 +7246,10 @@
     </row>
     <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="4">
-        <v>120955</v>
+        <v>422759</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C474" s="5" t="s">
         <v>482</v>
@@ -7218,10 +7257,10 @@
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
-        <v>1010000896</v>
+        <v>120955</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C475" s="5" t="s">
         <v>482</v>
@@ -7229,10 +7268,10 @@
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
-        <v>1010084308</v>
+        <v>1010000896</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C476" s="5" t="s">
         <v>482</v>
@@ -7240,54 +7279,54 @@
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
-        <v>1010084035</v>
-      </c>
-      <c r="B477" s="17" t="s">
-        <v>478</v>
+        <v>1010084308</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="C477" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="2">
+      <c r="A478" s="4">
+        <v>1010084035</v>
+      </c>
+      <c r="B478" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A479" s="2">
         <v>1010062826</v>
       </c>
-      <c r="B478" s="18" t="s">
+      <c r="B479" s="18" t="s">
         <v>483</v>
-      </c>
-      <c r="C478" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="15">
-        <v>1010002592</v>
-      </c>
-      <c r="B479" s="18" t="s">
-        <v>484</v>
       </c>
       <c r="C479" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="16">
-        <v>1010001155</v>
+      <c r="A480" s="15">
+        <v>1010002592</v>
       </c>
       <c r="B480" s="18" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C480" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="15">
-        <v>1010001062</v>
+      <c r="A481" s="16">
+        <v>1010001155</v>
       </c>
       <c r="B481" s="18" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C481" s="5" t="s">
         <v>491</v>
@@ -7295,32 +7334,32 @@
     </row>
     <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="15">
-        <v>1010084328</v>
+        <v>1010001062</v>
       </c>
       <c r="B482" s="18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C482" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="16">
-        <v>1010044502</v>
+      <c r="A483" s="15">
+        <v>1010084328</v>
       </c>
       <c r="B483" s="18" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C483" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="15">
-        <v>1010053692</v>
+      <c r="A484" s="16">
+        <v>1010044502</v>
       </c>
       <c r="B484" s="18" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C484" s="5" t="s">
         <v>491</v>
@@ -7328,18 +7367,25 @@
     </row>
     <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="15">
-        <v>390742</v>
+        <v>1010053692</v>
       </c>
       <c r="B485" s="18" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C485" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="2"/>
-      <c r="B486" s="2"/>
+      <c r="A486" s="15">
+        <v>390742</v>
+      </c>
+      <c r="B486" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
@@ -9127,7 +9173,7 @@
     </row>
     <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="2"/>
-      <c r="B933" s="1"/>
+      <c r="B933" s="2"/>
     </row>
     <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
@@ -9398,7 +9444,7 @@
       <c r="B1000" s="1"/>
     </row>
     <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1001" s="1"/>
+      <c r="A1001" s="2"/>
       <c r="B1001" s="1"/>
     </row>
     <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -10176,6 +10222,10 @@
     <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1195" s="1"/>
       <c r="B1195" s="1"/>
+    </row>
+    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1"/>
+      <c r="B1196" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecasPCM/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2E17758-BB04-42C7-8888-59074CD8A42F}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{429C1E01-1893-420A-88BA-65C206C1D183}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21990" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -2035,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1196"/>
+  <dimension ref="A1:F1196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -7321,7 +7321,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="16">
         <v>1010001155</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="15">
         <v>1010001062</v>
       </c>
@@ -7342,8 +7342,11 @@
       <c r="C482" s="5" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F482">
+        <v>390742</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" s="15">
         <v>1010084328</v>
       </c>
@@ -7354,7 +7357,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" s="16">
         <v>1010044502</v>
       </c>
@@ -7365,7 +7368,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="15">
         <v>1010053692</v>
       </c>
@@ -7376,9 +7379,9 @@
         <v>491</v>
       </c>
     </row>
-    <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="15">
-        <v>390742</v>
+        <v>1010083992</v>
       </c>
       <c r="B486" s="18" t="s">
         <v>490</v>
@@ -7387,43 +7390,43 @@
         <v>491</v>
       </c>
     </row>
-    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
     </row>
-    <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
     </row>
-    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
     </row>
-    <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
     </row>
-    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
     </row>
-    <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
     </row>
-    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
     </row>
-    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
     </row>
-    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
     </row>
-    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
     </row>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{429C1E01-1893-420A-88BA-65C206C1D183}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD1D7E13-2AA4-4FD8-B4D9-2EF7A76950C8}"/>
   <bookViews>
-    <workbookView xWindow="-21990" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -1693,7 +1693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1751,6 +1751,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1766,10 +1769,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2038,7 +2037,7 @@
   <dimension ref="A1:F1196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -5718,7 +5717,9 @@
       </c>
     </row>
     <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A335" s="4"/>
+      <c r="A335" s="21">
+        <v>1010086020</v>
+      </c>
       <c r="B335" s="4" t="s">
         <v>330</v>
       </c>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD1D7E13-2AA4-4FD8-B4D9-2EF7A76950C8}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711A64ED-D4C6-4BEF-B1F2-D9B798401254}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="493">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -1335,9 +1335,6 @@
     <t>ALONGADOR (EXTENSOR DE BICO)</t>
   </si>
   <si>
-    <t>BICO PNEU DIANTEIRA (RODA CAVALO)</t>
-  </si>
-  <si>
     <t>BICO PNEU (RODA FERRO CARRETA)</t>
   </si>
   <si>
@@ -1380,30 +1377,6 @@
     <t>PNEU BORRACHUDO NOVO</t>
   </si>
   <si>
-    <t>PNEU BORRACHUDO BONIN (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO BONIN (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO FOX  (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO FOX (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO VIPAL (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO VIPAL BANDA NOVA (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO VIPAL (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO VIPAL (RECAPADO) VT100</t>
-  </si>
-  <si>
     <t>RODA 22,5X8,25 295 10 FUROS</t>
   </si>
   <si>
@@ -1519,6 +1492,30 @@
   </si>
   <si>
     <t>PARAFUSO 10X60 (CUICA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNEU BORRACHUDO BONIN RT78 (RECAPADO) </t>
+  </si>
+  <si>
+    <t>PNEU LISO BONIN RT51 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU BORRACHUDO FOX TMD (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU LISO FOX BTL3B (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU LISO VIPAL VL110 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU LISO VIPAL BANDA NOVA VL130 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU BORRACHUDO VIPAL VRT2 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU BORRACHUDO VIPAL  VT100 (RECAPADO)</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1596,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1689,11 +1686,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1754,6 +1764,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1769,6 +1785,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2034,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1196"/>
+  <dimension ref="A1:F1195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2044,7 +2064,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>425</v>
@@ -2061,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2072,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2083,7 +2103,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2094,7 +2114,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2105,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2116,7 +2136,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2127,7 +2147,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2138,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2149,7 +2169,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2160,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2171,7 +2191,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2182,7 +2202,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2193,7 +2213,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2204,7 +2224,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2215,7 +2235,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2226,7 +2246,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2237,7 +2257,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2248,7 +2268,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2259,7 +2279,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2270,7 +2290,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2281,7 +2301,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2292,7 +2312,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2303,7 +2323,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2314,7 +2334,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2325,7 +2345,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2336,7 +2356,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2347,7 +2367,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2358,7 +2378,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2369,7 +2389,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2380,7 +2400,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2391,7 +2411,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2402,7 +2422,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2413,7 +2433,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2424,7 +2444,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2435,7 +2455,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2446,7 +2466,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2457,7 +2477,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2468,7 +2488,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2479,7 +2499,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2490,7 +2510,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2501,7 +2521,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2512,7 +2532,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2523,7 +2543,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2534,7 +2554,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2545,7 +2565,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2556,7 +2576,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2567,7 +2587,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2578,7 +2598,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2589,7 +2609,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2600,7 +2620,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2611,7 +2631,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2622,7 +2642,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2633,7 +2653,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2644,7 +2664,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2655,7 +2675,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2666,7 +2686,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2677,7 +2697,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2688,7 +2708,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2699,7 +2719,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2710,7 +2730,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2721,7 +2741,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2732,7 +2752,7 @@
         <v>61</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2743,7 +2763,7 @@
         <v>62</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2754,7 +2774,7 @@
         <v>63</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2765,7 +2785,7 @@
         <v>64</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2776,7 +2796,7 @@
         <v>65</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2787,7 +2807,7 @@
         <v>66</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2798,7 +2818,7 @@
         <v>67</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2809,7 +2829,7 @@
         <v>68</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2820,7 +2840,7 @@
         <v>69</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2831,7 +2851,7 @@
         <v>70</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2842,7 +2862,7 @@
         <v>71</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2853,7 +2873,7 @@
         <v>72</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2864,7 +2884,7 @@
         <v>428</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2875,7 +2895,7 @@
         <v>73</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2886,7 +2906,7 @@
         <v>74</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2897,7 +2917,7 @@
         <v>75</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2908,7 +2928,7 @@
         <v>76</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2919,7 +2939,7 @@
         <v>77</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2930,7 +2950,7 @@
         <v>78</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2941,7 +2961,7 @@
         <v>79</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2952,7 +2972,7 @@
         <v>80</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2963,7 +2983,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2974,7 +2994,7 @@
         <v>82</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2985,7 +3005,7 @@
         <v>83</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2996,7 +3016,7 @@
         <v>84</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3007,7 +3027,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3018,7 +3038,7 @@
         <v>86</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3029,7 +3049,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3040,7 +3060,7 @@
         <v>88</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3051,7 +3071,7 @@
         <v>89</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3062,7 +3082,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3073,7 +3093,7 @@
         <v>91</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3084,7 +3104,7 @@
         <v>92</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3095,7 +3115,7 @@
         <v>93</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3106,7 +3126,7 @@
         <v>94</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3117,7 +3137,7 @@
         <v>95</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3128,7 +3148,7 @@
         <v>96</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3139,7 +3159,7 @@
         <v>97</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3150,7 +3170,7 @@
         <v>98</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3161,7 +3181,7 @@
         <v>99</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3172,7 +3192,7 @@
         <v>100</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3183,7 +3203,7 @@
         <v>101</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3194,7 +3214,7 @@
         <v>102</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3205,7 +3225,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3216,7 +3236,7 @@
         <v>104</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3227,7 +3247,7 @@
         <v>105</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3238,7 +3258,7 @@
         <v>106</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3249,7 +3269,7 @@
         <v>107</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3260,7 +3280,7 @@
         <v>108</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3271,7 +3291,7 @@
         <v>109</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3282,7 +3302,7 @@
         <v>110</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3293,7 +3313,7 @@
         <v>111</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3304,7 +3324,7 @@
         <v>112</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3315,7 +3335,7 @@
         <v>113</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3326,7 +3346,7 @@
         <v>114</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3337,7 +3357,7 @@
         <v>115</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3348,7 +3368,7 @@
         <v>116</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3359,7 +3379,7 @@
         <v>117</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3370,7 +3390,7 @@
         <v>118</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3381,7 +3401,7 @@
         <v>119</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3392,7 +3412,7 @@
         <v>120</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3403,7 +3423,7 @@
         <v>121</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3414,7 +3434,7 @@
         <v>122</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3425,7 +3445,7 @@
         <v>123</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3436,7 +3456,7 @@
         <v>124</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3447,7 +3467,7 @@
         <v>125</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3458,7 +3478,7 @@
         <v>126</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3469,7 +3489,7 @@
         <v>127</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3480,7 +3500,7 @@
         <v>128</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3491,7 +3511,7 @@
         <v>129</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3502,7 +3522,7 @@
         <v>130</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3513,7 +3533,7 @@
         <v>131</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3524,7 +3544,7 @@
         <v>132</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3535,7 +3555,7 @@
         <v>133</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3546,7 +3566,7 @@
         <v>134</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3557,7 +3577,7 @@
         <v>135</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3568,7 +3588,7 @@
         <v>136</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3579,7 +3599,7 @@
         <v>137</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3590,7 +3610,7 @@
         <v>138</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3601,7 +3621,7 @@
         <v>139</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3612,7 +3632,7 @@
         <v>140</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3623,7 +3643,7 @@
         <v>141</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3634,7 +3654,7 @@
         <v>142</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3645,7 +3665,7 @@
         <v>143</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3656,7 +3676,7 @@
         <v>144</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3667,7 +3687,7 @@
         <v>145</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3678,7 +3698,7 @@
         <v>146</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3689,7 +3709,7 @@
         <v>147</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3700,7 +3720,7 @@
         <v>148</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3711,7 +3731,7 @@
         <v>149</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3722,7 +3742,7 @@
         <v>150</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3733,7 +3753,7 @@
         <v>151</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3744,7 +3764,7 @@
         <v>152</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3755,7 +3775,7 @@
         <v>153</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3766,7 +3786,7 @@
         <v>426</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3777,7 +3797,7 @@
         <v>427</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3788,7 +3808,7 @@
         <v>154</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3799,7 +3819,7 @@
         <v>155</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3810,7 +3830,7 @@
         <v>156</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3821,7 +3841,7 @@
         <v>157</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3832,7 +3852,7 @@
         <v>158</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3843,7 +3863,7 @@
         <v>159</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3854,7 +3874,7 @@
         <v>160</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3865,7 +3885,7 @@
         <v>161</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3876,7 +3896,7 @@
         <v>162</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3887,7 +3907,7 @@
         <v>163</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3898,7 +3918,7 @@
         <v>164</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3909,7 +3929,7 @@
         <v>165</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3920,7 +3940,7 @@
         <v>166</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3931,7 +3951,7 @@
         <v>167</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3942,7 +3962,7 @@
         <v>168</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3953,7 +3973,7 @@
         <v>169</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3964,7 +3984,7 @@
         <v>170</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3975,7 +3995,7 @@
         <v>171</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3986,7 +4006,7 @@
         <v>172</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3997,7 +4017,7 @@
         <v>173</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4008,7 +4028,7 @@
         <v>174</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4019,7 +4039,7 @@
         <v>175</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4030,7 +4050,7 @@
         <v>176</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4041,7 +4061,7 @@
         <v>177</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4052,7 +4072,7 @@
         <v>178</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4063,7 +4083,7 @@
         <v>179</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4074,7 +4094,7 @@
         <v>180</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4085,7 +4105,7 @@
         <v>181</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4096,7 +4116,7 @@
         <v>182</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4107,7 +4127,7 @@
         <v>183</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4118,7 +4138,7 @@
         <v>184</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4129,7 +4149,7 @@
         <v>185</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4140,7 +4160,7 @@
         <v>186</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4151,7 +4171,7 @@
         <v>187</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4162,7 +4182,7 @@
         <v>188</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4170,10 +4190,10 @@
         <v>1010055707</v>
       </c>
       <c r="B194" s="20" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4184,7 +4204,7 @@
         <v>189</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4195,7 +4215,7 @@
         <v>190</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4206,7 +4226,7 @@
         <v>191</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4217,7 +4237,7 @@
         <v>192</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4228,7 +4248,7 @@
         <v>193</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4239,7 +4259,7 @@
         <v>194</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4250,7 +4270,7 @@
         <v>195</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4261,7 +4281,7 @@
         <v>196</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4272,7 +4292,7 @@
         <v>197</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4283,7 +4303,7 @@
         <v>198</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4294,7 +4314,7 @@
         <v>199</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4305,7 +4325,7 @@
         <v>200</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4316,7 +4336,7 @@
         <v>201</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4327,7 +4347,7 @@
         <v>202</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4338,7 +4358,7 @@
         <v>203</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4349,7 +4369,7 @@
         <v>204</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4360,7 +4380,7 @@
         <v>205</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4371,7 +4391,7 @@
         <v>206</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4382,7 +4402,7 @@
         <v>207</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4393,7 +4413,7 @@
         <v>208</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4404,7 +4424,7 @@
         <v>209</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4415,7 +4435,7 @@
         <v>210</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4426,7 +4446,7 @@
         <v>211</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4437,7 +4457,7 @@
         <v>212</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4448,7 +4468,7 @@
         <v>213</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4459,7 +4479,7 @@
         <v>214</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4470,7 +4490,7 @@
         <v>215</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4481,7 +4501,7 @@
         <v>216</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4492,7 +4512,7 @@
         <v>217</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4503,7 +4523,7 @@
         <v>218</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4514,7 +4534,7 @@
         <v>219</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4525,7 +4545,7 @@
         <v>220</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4536,7 +4556,7 @@
         <v>221</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4547,7 +4567,7 @@
         <v>222</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4558,7 +4578,7 @@
         <v>223</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4569,7 +4589,7 @@
         <v>224</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4580,7 +4600,7 @@
         <v>225</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4591,7 +4611,7 @@
         <v>226</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4602,7 +4622,7 @@
         <v>227</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4613,7 +4633,7 @@
         <v>228</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4624,7 +4644,7 @@
         <v>229</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4635,7 +4655,7 @@
         <v>230</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4646,7 +4666,7 @@
         <v>231</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4657,7 +4677,7 @@
         <v>232</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4668,7 +4688,7 @@
         <v>233</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4679,7 +4699,7 @@
         <v>234</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4690,7 +4710,7 @@
         <v>235</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4701,7 +4721,7 @@
         <v>236</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4712,7 +4732,7 @@
         <v>237</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4723,7 +4743,7 @@
         <v>238</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4734,7 +4754,7 @@
         <v>239</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4745,7 +4765,7 @@
         <v>240</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4756,7 +4776,7 @@
         <v>241</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4767,7 +4787,7 @@
         <v>242</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4778,7 +4798,7 @@
         <v>243</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4789,7 +4809,7 @@
         <v>244</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4800,7 +4820,7 @@
         <v>245</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4811,7 +4831,7 @@
         <v>246</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4822,7 +4842,7 @@
         <v>247</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4833,7 +4853,7 @@
         <v>248</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4844,7 +4864,7 @@
         <v>249</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4855,7 +4875,7 @@
         <v>250</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4866,7 +4886,7 @@
         <v>251</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4877,7 +4897,7 @@
         <v>252</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4888,7 +4908,7 @@
         <v>253</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4899,7 +4919,7 @@
         <v>254</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4910,7 +4930,7 @@
         <v>255</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4921,7 +4941,7 @@
         <v>256</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4932,7 +4952,7 @@
         <v>257</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4943,7 +4963,7 @@
         <v>258</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4954,7 +4974,7 @@
         <v>259</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4965,7 +4985,7 @@
         <v>260</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4976,7 +4996,7 @@
         <v>261</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4987,7 +5007,7 @@
         <v>262</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4998,7 +5018,7 @@
         <v>263</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5009,7 +5029,7 @@
         <v>264</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5020,7 +5040,7 @@
         <v>265</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5031,7 +5051,7 @@
         <v>266</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5042,7 +5062,7 @@
         <v>267</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5053,7 +5073,7 @@
         <v>268</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5064,7 +5084,7 @@
         <v>269</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5075,7 +5095,7 @@
         <v>270</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5086,7 +5106,7 @@
         <v>271</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5097,7 +5117,7 @@
         <v>272</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5108,7 +5128,7 @@
         <v>273</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5119,7 +5139,7 @@
         <v>274</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5130,7 +5150,7 @@
         <v>275</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5141,7 +5161,7 @@
         <v>276</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5152,7 +5172,7 @@
         <v>277</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5163,7 +5183,7 @@
         <v>278</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5174,7 +5194,7 @@
         <v>279</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5185,7 +5205,7 @@
         <v>280</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5196,7 +5216,7 @@
         <v>281</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5207,7 +5227,7 @@
         <v>282</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5218,7 +5238,7 @@
         <v>283</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5229,7 +5249,7 @@
         <v>284</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5240,7 +5260,7 @@
         <v>285</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5251,7 +5271,7 @@
         <v>286</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5262,7 +5282,7 @@
         <v>287</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5273,7 +5293,7 @@
         <v>288</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5284,7 +5304,7 @@
         <v>289</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5295,7 +5315,7 @@
         <v>290</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5306,7 +5326,7 @@
         <v>291</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5317,7 +5337,7 @@
         <v>292</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5328,7 +5348,7 @@
         <v>293</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5339,7 +5359,7 @@
         <v>294</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5350,7 +5370,7 @@
         <v>295</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5361,7 +5381,7 @@
         <v>296</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5372,7 +5392,7 @@
         <v>297</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5383,7 +5403,7 @@
         <v>298</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5394,7 +5414,7 @@
         <v>299</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5405,7 +5425,7 @@
         <v>300</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5416,7 +5436,7 @@
         <v>301</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5427,7 +5447,7 @@
         <v>302</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5438,7 +5458,7 @@
         <v>304</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5449,7 +5469,7 @@
         <v>305</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5460,7 +5480,7 @@
         <v>306</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5471,7 +5491,7 @@
         <v>307</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5482,7 +5502,7 @@
         <v>308</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5493,7 +5513,7 @@
         <v>309</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5504,7 +5524,7 @@
         <v>310</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5515,7 +5535,7 @@
         <v>311</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5526,7 +5546,7 @@
         <v>312</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5537,7 +5557,7 @@
         <v>313</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5548,7 +5568,7 @@
         <v>314</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5559,7 +5579,7 @@
         <v>315</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5570,7 +5590,7 @@
         <v>316</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5581,7 +5601,7 @@
         <v>317</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5592,7 +5612,7 @@
         <v>318</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5603,7 +5623,7 @@
         <v>319</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5614,7 +5634,7 @@
         <v>320</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5625,7 +5645,7 @@
         <v>321</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5636,7 +5656,7 @@
         <v>322</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5647,7 +5667,7 @@
         <v>323</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5658,7 +5678,7 @@
         <v>324</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5669,7 +5689,7 @@
         <v>325</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5680,7 +5700,7 @@
         <v>326</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5691,7 +5711,7 @@
         <v>327</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5702,7 +5722,7 @@
         <v>328</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5713,7 +5733,7 @@
         <v>329</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5724,7 +5744,7 @@
         <v>330</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5735,7 +5755,7 @@
         <v>331</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5746,7 +5766,7 @@
         <v>332</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5757,7 +5777,7 @@
         <v>333</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5768,7 +5788,7 @@
         <v>334</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5779,7 +5799,7 @@
         <v>335</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5790,7 +5810,7 @@
         <v>336</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5801,7 +5821,7 @@
         <v>337</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5812,7 +5832,7 @@
         <v>338</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5823,7 +5843,7 @@
         <v>429</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5834,7 +5854,7 @@
         <v>339</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5845,7 +5865,7 @@
         <v>340</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5856,7 +5876,7 @@
         <v>341</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5867,7 +5887,7 @@
         <v>342</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5878,7 +5898,7 @@
         <v>343</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5889,7 +5909,7 @@
         <v>344</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5900,7 +5920,7 @@
         <v>345</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5911,7 +5931,7 @@
         <v>346</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5922,7 +5942,7 @@
         <v>347</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5933,7 +5953,7 @@
         <v>348</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5944,7 +5964,7 @@
         <v>349</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5955,7 +5975,7 @@
         <v>350</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5966,7 +5986,7 @@
         <v>351</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5977,7 +5997,7 @@
         <v>352</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5988,7 +6008,7 @@
         <v>353</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5999,7 +6019,7 @@
         <v>354</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6010,7 +6030,7 @@
         <v>355</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6021,7 +6041,7 @@
         <v>356</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6032,7 +6052,7 @@
         <v>357</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6043,7 +6063,7 @@
         <v>358</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6054,7 +6074,7 @@
         <v>359</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6065,7 +6085,7 @@
         <v>360</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6076,7 +6096,7 @@
         <v>361</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6087,7 +6107,7 @@
         <v>362</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6098,7 +6118,7 @@
         <v>363</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6109,7 +6129,7 @@
         <v>364</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6120,7 +6140,7 @@
         <v>365</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6131,7 +6151,7 @@
         <v>366</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6142,7 +6162,7 @@
         <v>367</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6153,7 +6173,7 @@
         <v>368</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6164,7 +6184,7 @@
         <v>369</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6175,7 +6195,7 @@
         <v>370</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6186,7 +6206,7 @@
         <v>371</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6197,7 +6217,7 @@
         <v>372</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6208,7 +6228,7 @@
         <v>373</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6219,7 +6239,7 @@
         <v>374</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6230,7 +6250,7 @@
         <v>375</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6241,7 +6261,7 @@
         <v>376</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6252,7 +6272,7 @@
         <v>377</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6263,7 +6283,7 @@
         <v>378</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6274,7 +6294,7 @@
         <v>379</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6285,7 +6305,7 @@
         <v>380</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6296,7 +6316,7 @@
         <v>381</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6307,7 +6327,7 @@
         <v>382</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6318,7 +6338,7 @@
         <v>383</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6329,7 +6349,7 @@
         <v>384</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6340,7 +6360,7 @@
         <v>385</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6351,7 +6371,7 @@
         <v>386</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6362,7 +6382,7 @@
         <v>387</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6373,7 +6393,7 @@
         <v>388</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6384,7 +6404,7 @@
         <v>389</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6395,7 +6415,7 @@
         <v>390</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6406,7 +6426,7 @@
         <v>391</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6417,7 +6437,7 @@
         <v>392</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6428,7 +6448,7 @@
         <v>393</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6439,7 +6459,7 @@
         <v>394</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6450,7 +6470,7 @@
         <v>395</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6461,7 +6481,7 @@
         <v>396</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6472,7 +6492,7 @@
         <v>397</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6483,7 +6503,7 @@
         <v>398</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6494,7 +6514,7 @@
         <v>399</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6505,7 +6525,7 @@
         <v>400</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6516,7 +6536,7 @@
         <v>401</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6527,7 +6547,7 @@
         <v>402</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6538,7 +6558,7 @@
         <v>403</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6549,7 +6569,7 @@
         <v>404</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6560,7 +6580,7 @@
         <v>405</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6571,7 +6591,7 @@
         <v>406</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6582,7 +6602,7 @@
         <v>407</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6593,7 +6613,7 @@
         <v>408</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6604,7 +6624,7 @@
         <v>409</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6615,7 +6635,7 @@
         <v>410</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6626,7 +6646,7 @@
         <v>411</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6637,7 +6657,7 @@
         <v>412</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6648,7 +6668,7 @@
         <v>413</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6659,7 +6679,7 @@
         <v>414</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6670,7 +6690,7 @@
         <v>415</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6681,7 +6701,7 @@
         <v>416</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6692,7 +6712,7 @@
         <v>417</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6703,7 +6723,7 @@
         <v>418</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6714,7 +6734,7 @@
         <v>419</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6725,7 +6745,7 @@
         <v>420</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6736,7 +6756,7 @@
         <v>421</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6747,7 +6767,7 @@
         <v>422</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6758,7 +6778,7 @@
         <v>423</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6769,7 +6789,7 @@
         <v>424</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6780,616 +6800,609 @@
         <v>431</v>
       </c>
       <c r="C431" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A432" s="15">
+        <v>1010058709</v>
+      </c>
+      <c r="B432" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A433" s="15">
+        <v>1010025711</v>
+      </c>
+      <c r="B433" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A434" s="15">
+        <v>1010059684</v>
+      </c>
+      <c r="B434" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C434" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A435" s="15">
+        <v>427341</v>
+      </c>
+      <c r="B435" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A436" s="15">
+        <v>1010085279</v>
+      </c>
+      <c r="B436" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C436" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A437" s="22">
+        <v>1010022588</v>
+      </c>
+      <c r="B437" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A438" s="15">
+        <v>1010026864</v>
+      </c>
+      <c r="B438" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A439" s="23">
+        <v>1010030946</v>
+      </c>
+      <c r="B439" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A440" s="23">
+        <v>1010022589</v>
+      </c>
+      <c r="B440" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A441" s="15">
+        <v>1040090143</v>
+      </c>
+      <c r="B441" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A442" s="15">
+        <v>1040090138</v>
+      </c>
+      <c r="B442" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A443" s="15">
+        <v>1030001314</v>
+      </c>
+      <c r="B443" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A444" s="15">
+        <v>1010052319</v>
+      </c>
+      <c r="B444" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A445" s="15">
+        <v>1010052320</v>
+      </c>
+      <c r="B445" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A446" s="15">
+        <v>1030000370</v>
+      </c>
+      <c r="B446" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="C446" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A447" s="15">
+        <v>1030000366</v>
+      </c>
+      <c r="B447" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A448" s="15">
+        <v>1030000368</v>
+      </c>
+      <c r="B448" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="C448" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A449" s="15">
+        <v>1030000369</v>
+      </c>
+      <c r="B449" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A450" s="15">
+        <v>1030000489</v>
+      </c>
+      <c r="B450" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A451" s="15">
+        <v>1030000490</v>
+      </c>
+      <c r="B451" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A452" s="15">
+        <v>1030000821</v>
+      </c>
+      <c r="B452" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="C452" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A453" s="15">
+        <v>1030000511</v>
+      </c>
+      <c r="B453" s="22" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="4">
-        <v>1010034964</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C432" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A433" s="4">
-        <v>1010058709</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="C433" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A434" s="4">
-        <v>1010025711</v>
-      </c>
-      <c r="B434" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C434" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A435" s="4">
-        <v>1010059684</v>
-      </c>
-      <c r="B435" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="C435" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A436" s="4">
-        <v>427341</v>
-      </c>
-      <c r="B436" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="C436" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="4">
-        <v>1010085279</v>
-      </c>
-      <c r="B437" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="C437" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="4">
-        <v>1010022588</v>
-      </c>
-      <c r="B438" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="C438" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="4">
-        <v>1010026864</v>
-      </c>
-      <c r="B439" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="C439" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A440" s="4">
-        <v>1010030946</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="C440" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="4">
-        <v>1010022589</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="C441" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A442" s="4">
-        <v>1040090143</v>
-      </c>
-      <c r="B442" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="C442" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="4">
-        <v>1040090138</v>
-      </c>
-      <c r="B443" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C443" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A444" s="4">
-        <v>1030001314</v>
-      </c>
-      <c r="B444" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="C444" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="4">
-        <v>1010052319</v>
-      </c>
-      <c r="B445" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C445" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="4">
-        <v>1010052320</v>
-      </c>
-      <c r="B446" s="4" t="s">
+      <c r="C453" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A454" s="18">
+        <v>1010084279</v>
+      </c>
+      <c r="B454" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="C446" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A447" s="4">
-        <v>1030000370</v>
-      </c>
-      <c r="B447" s="4" t="s">
+      <c r="C454" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A455" s="18">
+        <v>1010004281</v>
+      </c>
+      <c r="B455" s="15" t="s">
         <v>447</v>
       </c>
-      <c r="C447" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="4">
-        <v>1030000366</v>
-      </c>
-      <c r="B448" s="4" t="s">
+      <c r="C455" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A456" s="15">
+        <v>1010022118</v>
+      </c>
+      <c r="B456" s="23" t="s">
         <v>448</v>
       </c>
-      <c r="C448" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="4">
-        <v>1030000368</v>
-      </c>
-      <c r="B449" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="C449" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A450" s="4">
-        <v>1030000369</v>
-      </c>
-      <c r="B450" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="4">
-        <v>1030000489</v>
-      </c>
-      <c r="B451" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="4">
-        <v>1030000490</v>
-      </c>
-      <c r="B452" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C452" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="4">
-        <v>1030000821</v>
-      </c>
-      <c r="B453" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="4">
-        <v>1030000511</v>
-      </c>
-      <c r="B454" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="C454" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A455" s="4">
-        <v>1010084279</v>
-      </c>
-      <c r="B455" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="C455" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="4">
-        <v>1010004281</v>
-      </c>
-      <c r="B456" s="4" t="s">
-        <v>456</v>
-      </c>
       <c r="C456" s="5" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
-        <v>1010022118</v>
+        <v>1010028657</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="4">
-        <v>1010028657</v>
+      <c r="A458" s="8">
+        <v>1010028655</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="8">
-        <v>1010028655</v>
+        <v>145165</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="8">
-        <v>145165</v>
+      <c r="A460" s="4">
+        <v>51666</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="4">
-        <v>51666</v>
+      <c r="A461" s="8">
+        <v>1010080930</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="8">
-        <v>1010080930</v>
+      <c r="A462" s="4">
+        <v>161055</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
-        <v>161055</v>
+        <v>1010050517</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
-        <v>1010050517</v>
+        <v>1010084190</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
-        <v>1010084190</v>
+        <v>1010084195</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
-        <v>1010084195</v>
+        <v>1010001400</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="4">
-        <v>1010001400</v>
+      <c r="A467" s="8">
+        <v>1010008416</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="8">
-        <v>1010008416</v>
+      <c r="A468" s="13">
+        <v>1010018372</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="13">
-        <v>1010018372</v>
+        <v>1010018361</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="13">
-        <v>1010018361</v>
-      </c>
-      <c r="B470" s="4" t="s">
-        <v>470</v>
+      <c r="A470" s="4">
+        <v>1010055398</v>
+      </c>
+      <c r="B470" s="8" t="s">
+        <v>462</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
-        <v>1010055398</v>
-      </c>
-      <c r="B471" s="8" t="s">
-        <v>471</v>
+        <v>422131</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>463</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
-        <v>422131</v>
+        <v>1010084370</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
-        <v>1010084370</v>
+        <v>422759</v>
       </c>
       <c r="B473" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C473" s="5" t="s">
         <v>473</v>
-      </c>
-      <c r="C473" s="5" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="4">
-        <v>422759</v>
+        <v>120955</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
-        <v>120955</v>
+        <v>1010000896</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
-        <v>1010000896</v>
+        <v>1010084308</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
-        <v>1010084308</v>
-      </c>
-      <c r="B477" s="4" t="s">
-        <v>477</v>
+        <v>1010084035</v>
+      </c>
+      <c r="B477" s="17" t="s">
+        <v>469</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="4">
-        <v>1010084035</v>
-      </c>
-      <c r="B478" s="17" t="s">
-        <v>478</v>
+      <c r="A478" s="2">
+        <v>1010062826</v>
+      </c>
+      <c r="B478" s="18" t="s">
+        <v>474</v>
       </c>
       <c r="C478" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="2">
-        <v>1010062826</v>
+      <c r="A479" s="15">
+        <v>1010002592</v>
       </c>
       <c r="B479" s="18" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="15">
-        <v>1010002592</v>
+      <c r="A480" s="16">
+        <v>1010001155</v>
       </c>
       <c r="B480" s="18" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="481" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="16">
-        <v>1010001155</v>
+      <c r="A481" s="15">
+        <v>1010001062</v>
       </c>
       <c r="B481" s="18" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
+      </c>
+      <c r="F481">
+        <v>390742</v>
       </c>
     </row>
     <row r="482" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="15">
-        <v>1010001062</v>
+        <v>1010084328</v>
       </c>
       <c r="B482" s="18" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="F482">
-        <v>390742</v>
+        <v>482</v>
       </c>
     </row>
     <row r="483" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="15">
-        <v>1010084328</v>
+      <c r="A483" s="16">
+        <v>1010044502</v>
       </c>
       <c r="B483" s="18" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="484" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="16">
-        <v>1010044502</v>
+      <c r="A484" s="15">
+        <v>1010053692</v>
       </c>
       <c r="B484" s="18" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="485" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="15">
-        <v>1010053692</v>
+        <v>1010083992</v>
       </c>
       <c r="B485" s="18" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="486" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="15">
-        <v>1010083992</v>
-      </c>
-      <c r="B486" s="18" t="s">
-        <v>490</v>
-      </c>
-      <c r="C486" s="5" t="s">
-        <v>491</v>
-      </c>
+      <c r="A486" s="2"/>
+      <c r="B486" s="2"/>
     </row>
     <row r="487" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
@@ -9177,7 +9190,7 @@
     </row>
     <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="2"/>
-      <c r="B933" s="2"/>
+      <c r="B933" s="1"/>
     </row>
     <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
@@ -9448,7 +9461,7 @@
       <c r="B1000" s="1"/>
     </row>
     <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1001" s="2"/>
+      <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
     </row>
     <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -10226,10 +10239,6 @@
     <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1195" s="1"/>
       <c r="B1195" s="1"/>
-    </row>
-    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1196" s="1"/>
-      <c r="B1196" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711A64ED-D4C6-4BEF-B1F2-D9B798401254}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9A201A7-C932-4E28-81A6-C6DAF90CC12E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="494">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -1516,6 +1516,9 @@
   </si>
   <si>
     <t>PNEU BORRACHUDO VIPAL  VT100 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>TERMINAL ISOL AUTOTRAC (CONECTOR PARA RELE 24V)</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1195"/>
+  <dimension ref="A1:F1196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -6783,32 +6786,32 @@
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="4">
-        <v>1040017204</v>
+        <v>1010031690</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>424</v>
+        <v>493</v>
       </c>
       <c r="C430" s="5" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="6">
+      <c r="A431" s="4">
+        <v>1040017204</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A432" s="6">
         <v>1010022119</v>
       </c>
-      <c r="B431" s="6" t="s">
+      <c r="B432" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="C431" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="15">
-        <v>1010058709</v>
-      </c>
-      <c r="B432" s="15" t="s">
-        <v>432</v>
       </c>
       <c r="C432" s="5" t="s">
         <v>483</v>
@@ -6816,10 +6819,10 @@
     </row>
     <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="15">
-        <v>1010025711</v>
+        <v>1010058709</v>
       </c>
       <c r="B433" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C433" s="5" t="s">
         <v>483</v>
@@ -6827,10 +6830,10 @@
     </row>
     <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="15">
-        <v>1010059684</v>
+        <v>1010025711</v>
       </c>
       <c r="B434" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C434" s="5" t="s">
         <v>483</v>
@@ -6838,10 +6841,10 @@
     </row>
     <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="15">
-        <v>427341</v>
+        <v>1010059684</v>
       </c>
       <c r="B435" s="15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C435" s="5" t="s">
         <v>483</v>
@@ -6849,43 +6852,43 @@
     </row>
     <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="15">
-        <v>1010085279</v>
+        <v>427341</v>
       </c>
       <c r="B436" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C436" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="22">
-        <v>1010022588</v>
+      <c r="A437" s="15">
+        <v>1010085279</v>
       </c>
       <c r="B437" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C437" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="15">
-        <v>1010026864</v>
-      </c>
-      <c r="B438" s="20" t="s">
-        <v>438</v>
+      <c r="A438" s="22">
+        <v>1010022588</v>
+      </c>
+      <c r="B438" s="15" t="s">
+        <v>437</v>
       </c>
       <c r="C438" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="23">
-        <v>1010030946</v>
+      <c r="A439" s="15">
+        <v>1010026864</v>
       </c>
       <c r="B439" s="20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C439" s="5" t="s">
         <v>483</v>
@@ -6893,21 +6896,21 @@
     </row>
     <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="23">
-        <v>1010022589</v>
-      </c>
-      <c r="B440" s="15" t="s">
-        <v>440</v>
+        <v>1010030946</v>
+      </c>
+      <c r="B440" s="20" t="s">
+        <v>439</v>
       </c>
       <c r="C440" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="15">
-        <v>1040090143</v>
+      <c r="A441" s="23">
+        <v>1010022589</v>
       </c>
       <c r="B441" s="15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C441" s="5" t="s">
         <v>483</v>
@@ -6915,10 +6918,10 @@
     </row>
     <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="15">
-        <v>1040090138</v>
+        <v>1040090143</v>
       </c>
       <c r="B442" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C442" s="5" t="s">
         <v>483</v>
@@ -6926,10 +6929,10 @@
     </row>
     <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="15">
-        <v>1030001314</v>
+        <v>1040090138</v>
       </c>
       <c r="B443" s="15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C443" s="5" t="s">
         <v>483</v>
@@ -6937,10 +6940,10 @@
     </row>
     <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="15">
-        <v>1010052319</v>
+        <v>1030001314</v>
       </c>
       <c r="B444" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C444" s="5" t="s">
         <v>483</v>
@@ -6948,10 +6951,10 @@
     </row>
     <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="15">
-        <v>1010052320</v>
+        <v>1010052319</v>
       </c>
       <c r="B445" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C445" s="5" t="s">
         <v>483</v>
@@ -6959,10 +6962,10 @@
     </row>
     <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="15">
-        <v>1030000370</v>
+        <v>1010052320</v>
       </c>
       <c r="B446" s="15" t="s">
-        <v>485</v>
+        <v>445</v>
       </c>
       <c r="C446" s="5" t="s">
         <v>483</v>
@@ -6970,10 +6973,10 @@
     </row>
     <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="15">
-        <v>1030000366</v>
+        <v>1030000370</v>
       </c>
       <c r="B447" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C447" s="5" t="s">
         <v>483</v>
@@ -6981,10 +6984,10 @@
     </row>
     <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="15">
-        <v>1030000368</v>
+        <v>1030000366</v>
       </c>
       <c r="B448" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C448" s="5" t="s">
         <v>483</v>
@@ -6992,10 +6995,10 @@
     </row>
     <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="15">
-        <v>1030000369</v>
+        <v>1030000368</v>
       </c>
       <c r="B449" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C449" s="5" t="s">
         <v>483</v>
@@ -7003,10 +7006,10 @@
     </row>
     <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="15">
-        <v>1030000489</v>
+        <v>1030000369</v>
       </c>
       <c r="B450" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C450" s="5" t="s">
         <v>483</v>
@@ -7014,10 +7017,10 @@
     </row>
     <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="15">
-        <v>1030000490</v>
+        <v>1030000489</v>
       </c>
       <c r="B451" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C451" s="5" t="s">
         <v>483</v>
@@ -7025,10 +7028,10 @@
     </row>
     <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="15">
-        <v>1030000821</v>
+        <v>1030000490</v>
       </c>
       <c r="B452" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C452" s="5" t="s">
         <v>483</v>
@@ -7036,21 +7039,21 @@
     </row>
     <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="15">
-        <v>1030000511</v>
-      </c>
-      <c r="B453" s="22" t="s">
-        <v>492</v>
+        <v>1030000821</v>
+      </c>
+      <c r="B453" s="15" t="s">
+        <v>491</v>
       </c>
       <c r="C453" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="18">
-        <v>1010084279</v>
+      <c r="A454" s="15">
+        <v>1030000511</v>
       </c>
       <c r="B454" s="22" t="s">
-        <v>446</v>
+        <v>492</v>
       </c>
       <c r="C454" s="5" t="s">
         <v>483</v>
@@ -7058,43 +7061,43 @@
     </row>
     <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="18">
-        <v>1010004281</v>
-      </c>
-      <c r="B455" s="15" t="s">
-        <v>447</v>
+        <v>1010084279</v>
+      </c>
+      <c r="B455" s="22" t="s">
+        <v>446</v>
       </c>
       <c r="C455" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="15">
-        <v>1010022118</v>
-      </c>
-      <c r="B456" s="23" t="s">
-        <v>448</v>
+      <c r="A456" s="18">
+        <v>1010004281</v>
+      </c>
+      <c r="B456" s="15" t="s">
+        <v>447</v>
       </c>
       <c r="C456" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="4">
+      <c r="A457" s="15">
+        <v>1010022118</v>
+      </c>
+      <c r="B457" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A458" s="4">
         <v>1010028657</v>
       </c>
-      <c r="B457" s="4" t="s">
+      <c r="B458" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="C457" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="8">
-        <v>1010028655</v>
-      </c>
-      <c r="B458" s="4" t="s">
-        <v>450</v>
       </c>
       <c r="C458" s="5" t="s">
         <v>473</v>
@@ -7102,43 +7105,43 @@
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="8">
-        <v>145165</v>
+        <v>1010028655</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C459" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="4">
-        <v>51666</v>
+      <c r="A460" s="8">
+        <v>145165</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C460" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="8">
-        <v>1010080930</v>
+      <c r="A461" s="4">
+        <v>51666</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C461" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="4">
-        <v>161055</v>
+      <c r="A462" s="8">
+        <v>1010080930</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C462" s="5" t="s">
         <v>473</v>
@@ -7146,10 +7149,10 @@
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
-        <v>1010050517</v>
+        <v>161055</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C463" s="5" t="s">
         <v>473</v>
@@ -7157,10 +7160,10 @@
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
-        <v>1010084190</v>
+        <v>1010050517</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C464" s="5" t="s">
         <v>473</v>
@@ -7168,10 +7171,10 @@
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
-        <v>1010084195</v>
+        <v>1010084190</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C465" s="5" t="s">
         <v>473</v>
@@ -7179,32 +7182,32 @@
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
-        <v>1010001400</v>
+        <v>1010084195</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C466" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="8">
-        <v>1010008416</v>
+      <c r="A467" s="4">
+        <v>1010001400</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C467" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="13">
-        <v>1010018372</v>
+      <c r="A468" s="8">
+        <v>1010008416</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C468" s="5" t="s">
         <v>473</v>
@@ -7212,21 +7215,21 @@
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="13">
-        <v>1010018361</v>
+        <v>1010018372</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C469" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="4">
-        <v>1010055398</v>
-      </c>
-      <c r="B470" s="8" t="s">
-        <v>462</v>
+      <c r="A470" s="13">
+        <v>1010018361</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>461</v>
       </c>
       <c r="C470" s="5" t="s">
         <v>473</v>
@@ -7234,10 +7237,10 @@
     </row>
     <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
-        <v>422131</v>
-      </c>
-      <c r="B471" s="4" t="s">
-        <v>463</v>
+        <v>1010055398</v>
+      </c>
+      <c r="B471" s="8" t="s">
+        <v>462</v>
       </c>
       <c r="C471" s="5" t="s">
         <v>473</v>
@@ -7245,10 +7248,10 @@
     </row>
     <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
-        <v>1010084370</v>
+        <v>422131</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C472" s="5" t="s">
         <v>473</v>
@@ -7256,10 +7259,10 @@
     </row>
     <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
-        <v>422759</v>
+        <v>1010084370</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C473" s="5" t="s">
         <v>473</v>
@@ -7267,10 +7270,10 @@
     </row>
     <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="4">
-        <v>120955</v>
+        <v>422759</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C474" s="5" t="s">
         <v>473</v>
@@ -7278,10 +7281,10 @@
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
-        <v>1010000896</v>
+        <v>120955</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C475" s="5" t="s">
         <v>473</v>
@@ -7289,10 +7292,10 @@
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
-        <v>1010084308</v>
+        <v>1010000896</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C476" s="5" t="s">
         <v>473</v>
@@ -7300,90 +7303,90 @@
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
-        <v>1010084035</v>
-      </c>
-      <c r="B477" s="17" t="s">
-        <v>469</v>
+        <v>1010084308</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>468</v>
       </c>
       <c r="C477" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="2">
+      <c r="A478" s="4">
+        <v>1010084035</v>
+      </c>
+      <c r="B478" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A479" s="2">
         <v>1010062826</v>
       </c>
-      <c r="B478" s="18" t="s">
+      <c r="B479" s="18" t="s">
         <v>474</v>
-      </c>
-      <c r="C478" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="15">
-        <v>1010002592</v>
-      </c>
-      <c r="B479" s="18" t="s">
-        <v>475</v>
       </c>
       <c r="C479" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="16">
-        <v>1010001155</v>
+      <c r="A480" s="15">
+        <v>1010002592</v>
       </c>
       <c r="B480" s="18" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C480" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="481" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="15">
-        <v>1010001062</v>
+      <c r="A481" s="16">
+        <v>1010001155</v>
       </c>
       <c r="B481" s="18" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C481" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="F481">
-        <v>390742</v>
-      </c>
     </row>
     <row r="482" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="15">
-        <v>1010084328</v>
+        <v>1010001062</v>
       </c>
       <c r="B482" s="18" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C482" s="5" t="s">
         <v>482</v>
       </c>
+      <c r="F482">
+        <v>390742</v>
+      </c>
     </row>
     <row r="483" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="16">
-        <v>1010044502</v>
+      <c r="A483" s="15">
+        <v>1010084328</v>
       </c>
       <c r="B483" s="18" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C483" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="484" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="15">
-        <v>1010053692</v>
+      <c r="A484" s="16">
+        <v>1010044502</v>
       </c>
       <c r="B484" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C484" s="5" t="s">
         <v>482</v>
@@ -7391,18 +7394,25 @@
     </row>
     <row r="485" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="15">
-        <v>1010083992</v>
+        <v>1010053692</v>
       </c>
       <c r="B485" s="18" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C485" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="486" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="2"/>
-      <c r="B486" s="2"/>
+      <c r="A486" s="15">
+        <v>1010083992</v>
+      </c>
+      <c r="B486" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="487" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
@@ -9190,7 +9200,7 @@
     </row>
     <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="2"/>
-      <c r="B933" s="1"/>
+      <c r="B933" s="2"/>
     </row>
     <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
@@ -9461,7 +9471,7 @@
       <c r="B1000" s="1"/>
     </row>
     <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1001" s="1"/>
+      <c r="A1001" s="2"/>
       <c r="B1001" s="1"/>
     </row>
     <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -10239,6 +10249,10 @@
     <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1195" s="1"/>
       <c r="B1195" s="1"/>
+    </row>
+    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1"/>
+      <c r="B1196" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
